--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAFDCBB-0694-465D-AD5D-69B5BE080E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF005C6-56F5-4CC1-91E7-900E5063907E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="116">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -376,6 +376,12 @@
   </si>
   <si>
     <t>Spende Muttertagsbasteln</t>
+  </si>
+  <si>
+    <t>tzgl  12.5.</t>
+  </si>
+  <si>
+    <t>tzgl  26.5.</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1057,27 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="58">
+  <dxfs count="62">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -3882,17 +3908,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="54">
+    <format dxfId="58">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3996,17 +4022,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="57">
+    <format dxfId="61">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6062,30 +6088,46 @@
       <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="14"/>
+      <c r="A41" s="14">
+        <v>46168</v>
+      </c>
       <c r="B41" s="15">
         <v>37</v>
       </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="18"/>
+      <c r="C41" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
+      <c r="H41" s="17">
+        <v>108</v>
+      </c>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
     <row r="42" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="14"/>
+      <c r="A42" s="14">
+        <v>46174</v>
+      </c>
       <c r="B42" s="15">
         <v>38</v>
       </c>
-      <c r="C42" s="15"/>
-      <c r="D42" s="18"/>
+      <c r="C42" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E42" s="16"/>
       <c r="F42" s="17"/>
       <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
+      <c r="H42" s="17">
+        <v>80</v>
+      </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
     </row>
@@ -6132,30 +6174,16 @@
       <c r="J45" s="2"/>
     </row>
     <row r="46" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="14"/>
       <c r="B46" s="15">
         <v>42</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
     </row>
     <row r="47" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="14"/>
       <c r="B47" s="15">
         <v>43</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
     </row>
@@ -7057,7 +7085,7 @@
       </c>
       <c r="H111" s="26">
         <f>SUM(H3:H110)</f>
-        <v>6502.11</v>
+        <v>6690.11</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -7087,7 +7115,7 @@
       </c>
       <c r="F113" s="26">
         <f>F111+Ausgaben!G178</f>
-        <v>2015.6300000000251</v>
+        <v>1862.6400000000253</v>
       </c>
       <c r="G113" s="26">
         <f>G111+Ausgaben!H178</f>
@@ -7095,7 +7123,7 @@
       </c>
       <c r="H113" s="26">
         <f>H111+Ausgaben!I178</f>
-        <v>3295.7</v>
+        <v>3483.7</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
@@ -7120,7 +7148,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>7311.8300000000254</v>
+        <v>7346.8400000000256</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -7855,138 +7883,138 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C99:D100">
-    <cfRule type="cellIs" dxfId="51" priority="62" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C99:D100 H34:H40 H48:H110 G41:H45">
+    <cfRule type="cellIs" dxfId="55" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97 H34:H110">
-    <cfRule type="cellIs" dxfId="50" priority="67" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97">
+    <cfRule type="cellIs" dxfId="54" priority="68" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D31 D41:D61">
-    <cfRule type="cellIs" dxfId="49" priority="5" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D20:D22 D31 D41:D45 D48:D61">
+    <cfRule type="cellIs" dxfId="53" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D89">
-    <cfRule type="cellIs" dxfId="48" priority="26" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:F82">
-    <cfRule type="cellIs" dxfId="47" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:G81">
-    <cfRule type="cellIs" dxfId="46" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101:G110">
-    <cfRule type="cellIs" dxfId="45" priority="60" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="44" priority="87" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="88" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41:F42">
-    <cfRule type="cellIs" dxfId="43" priority="25" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E41:F41">
+    <cfRule type="cellIs" dxfId="47" priority="48" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46:F46">
-    <cfRule type="cellIs" dxfId="42" priority="47" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G41:G47 E34:G37 G38 E39:G40">
-    <cfRule type="cellIs" dxfId="41" priority="49" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E34:G37 G38 E39:G40">
+    <cfRule type="cellIs" dxfId="46" priority="50" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:G49 G50:G51 E51:F51 F52:G52 G53:G58">
-    <cfRule type="cellIs" dxfId="40" priority="107" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="108" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E69:G71 G82:G83">
-    <cfRule type="cellIs" dxfId="39" priority="81" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="82" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E84:G89 D90:G98">
-    <cfRule type="cellIs" dxfId="38" priority="63" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:H3">
-    <cfRule type="cellIs" dxfId="37" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:H32">
-    <cfRule type="cellIs" dxfId="36" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:G25">
-    <cfRule type="cellIs" dxfId="35" priority="282" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="283" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:G60">
-    <cfRule type="cellIs" dxfId="34" priority="24" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72:G72">
-    <cfRule type="cellIs" dxfId="33" priority="79" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="80" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A93:C93">
-    <cfRule type="cellIs" dxfId="32" priority="195" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="196" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="cellIs" dxfId="31" priority="279" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="280" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
-    <cfRule type="cellIs" dxfId="30" priority="361" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="362" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H22">
-    <cfRule type="cellIs" dxfId="29" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:H31 G33:H33">
-    <cfRule type="cellIs" dxfId="28" priority="56" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="57" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10 B83">
-    <cfRule type="cellIs" dxfId="27" priority="209" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="210" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H27">
-    <cfRule type="cellIs" dxfId="26" priority="3" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="4" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E42:F42">
+    <cfRule type="cellIs" dxfId="30" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D28 D31:D110" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D28 D48:D110 D31:D45" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$J$1:$J$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -9860,14 +9888,22 @@
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="41"/>
-      <c r="B76" s="14"/>
+      <c r="B76" s="14">
+        <v>46168</v>
+      </c>
       <c r="C76" s="48">
         <v>72</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="E76" s="82"/>
+      <c r="D76" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E76" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F76" s="19"/>
-      <c r="G76" s="20"/>
+      <c r="G76" s="20">
+        <v>-4.99</v>
+      </c>
       <c r="H76" s="20"/>
       <c r="I76" s="20"/>
       <c r="J76" s="4"/>
@@ -9876,14 +9912,22 @@
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="41"/>
-      <c r="B77" s="14"/>
+      <c r="B77" s="14">
+        <v>46174</v>
+      </c>
       <c r="C77" s="48">
         <v>73</v>
       </c>
-      <c r="D77" s="3"/>
-      <c r="E77" s="82"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="20"/>
+      <c r="D77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" s="16"/>
+      <c r="G77" s="20">
+        <v>-12</v>
+      </c>
       <c r="H77" s="20"/>
       <c r="I77" s="20"/>
       <c r="J77" s="4"/>
@@ -9892,14 +9936,22 @@
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="41"/>
-      <c r="B78" s="14"/>
+      <c r="B78" s="14">
+        <v>46175</v>
+      </c>
       <c r="C78" s="48">
         <v>74</v>
       </c>
-      <c r="D78" s="3"/>
-      <c r="E78" s="82"/>
+      <c r="D78" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E78" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F78" s="19"/>
-      <c r="G78" s="20"/>
+      <c r="G78" s="20">
+        <v>-47</v>
+      </c>
       <c r="H78" s="20"/>
       <c r="I78" s="20"/>
       <c r="J78" s="4"/>
@@ -9908,14 +9960,22 @@
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="41"/>
-      <c r="B79" s="14"/>
+      <c r="B79" s="14">
+        <v>46175</v>
+      </c>
       <c r="C79" s="48">
         <v>75</v>
       </c>
-      <c r="D79" s="3"/>
-      <c r="E79" s="82"/>
+      <c r="D79" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E79" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F79" s="19"/>
-      <c r="G79" s="20"/>
+      <c r="G79" s="20">
+        <v>-89</v>
+      </c>
       <c r="H79" s="20"/>
       <c r="I79" s="20"/>
       <c r="J79" s="4"/>
@@ -11504,7 +11564,7 @@
       </c>
       <c r="G178" s="32">
         <f>SUM(G3:G177)</f>
-        <v>-3930.7499999999986</v>
+        <v>-4083.7399999999984</v>
       </c>
       <c r="H178" s="32">
         <f>SUM(H3:H177)</f>
@@ -12425,132 +12485,152 @@
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A242 E33 E76:E123 E133:E144">
-    <cfRule type="cellIs" dxfId="25" priority="490" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A3:A242 E33 E80:E123 E133:E144">
+    <cfRule type="cellIs" dxfId="29" priority="494" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129:B142">
-    <cfRule type="cellIs" dxfId="24" priority="473" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="477" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156:B244">
-    <cfRule type="cellIs" dxfId="23" priority="30" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="34" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C155 C157 C159 C161 C163 C165 C167 C173 C175">
-    <cfRule type="cellIs" dxfId="22" priority="31" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="35" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C243 J179 I179:I244">
-    <cfRule type="cellIs" dxfId="21" priority="720" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="724" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D132">
-    <cfRule type="cellIs" dxfId="20" priority="488" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="492" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D149">
-    <cfRule type="cellIs" dxfId="19" priority="75" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="79" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D153:D154">
-    <cfRule type="cellIs" dxfId="18" priority="459" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="463" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D158:D163">
-    <cfRule type="cellIs" dxfId="17" priority="16" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="20" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:E165 D166:D167 C169:D169 D170:E170 C171:D171">
-    <cfRule type="cellIs" dxfId="16" priority="23" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D177:E179">
-    <cfRule type="cellIs" dxfId="15" priority="25" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D179:H242">
-    <cfRule type="cellIs" dxfId="14" priority="672" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="676" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E125:E131 E146:E163">
-    <cfRule type="cellIs" dxfId="13" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="15" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="12" priority="7" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="11" priority="8" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
+    <cfRule type="cellIs" dxfId="14" priority="10" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E58:E59">
+    <cfRule type="cellIs" dxfId="13" priority="9" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61">
+    <cfRule type="cellIs" dxfId="12" priority="8" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E64">
+    <cfRule type="cellIs" dxfId="11" priority="7" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E66:E68">
     <cfRule type="cellIs" dxfId="10" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E59">
+  <conditionalFormatting sqref="E72">
     <cfRule type="cellIs" dxfId="9" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E61">
-    <cfRule type="cellIs" dxfId="8" priority="4" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E64">
-    <cfRule type="cellIs" dxfId="7" priority="3" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E166:E169">
-    <cfRule type="cellIs" dxfId="6" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:E176">
-    <cfRule type="cellIs" dxfId="5" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="16" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="4" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="14" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="cellIs" dxfId="3" priority="133" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="137" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="cellIs" dxfId="2" priority="17" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="21" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E66:E68">
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E76">
+    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72">
+  <conditionalFormatting sqref="E77">
+    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F77">
+    <cfRule type="cellIs" dxfId="1" priority="3" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E78:E79">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF005C6-56F5-4CC1-91E7-900E5063907E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBC7371-602D-47C3-A385-A33FB7D1C762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,9 +18,9 @@
     <sheet name="Gesamt" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Ausgaben!$B$2:$J$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Ausgaben!$B$2:$J$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Einnahmen!$A$2:$H$107</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Ausgaben!$A$1:$I$177</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Ausgaben!$A$1:$I$178</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Einnahmen!$A$1:$H$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="125">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -382,6 +382,33 @@
   </si>
   <si>
     <t>tzgl  26.5.</t>
+  </si>
+  <si>
+    <t>tzgl 9.6.</t>
+  </si>
+  <si>
+    <t>AWO Bund</t>
+  </si>
+  <si>
+    <t>Awo Open 23.6.</t>
+  </si>
+  <si>
+    <t>tzgl 23.6.</t>
+  </si>
+  <si>
+    <t>SPD Getränke Ferdi</t>
+  </si>
+  <si>
+    <t>Spende an Ponde</t>
+  </si>
+  <si>
+    <t>Spende an Awo Waldheim</t>
+  </si>
+  <si>
+    <t>AwoOpen</t>
+  </si>
+  <si>
+    <t>80a</t>
   </si>
 </sst>
 </file>
@@ -1057,17 +1084,7 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="62">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="60">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1518,7 +1535,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bernd Wild" refreshedDate="45318.474550578707" createdVersion="4" refreshedVersion="8" minRefreshableVersion="3" recordCount="168" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="E2:I173" sheet="Ausgaben"/>
+    <worksheetSource ref="E2:I174" sheet="Ausgaben"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="Zweck II" numFmtId="0">
@@ -3908,17 +3925,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="58">
+    <format dxfId="56">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4022,17 +4039,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="61">
+    <format dxfId="59">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6132,70 +6149,132 @@
       <c r="J42" s="2"/>
     </row>
     <row r="43" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="14"/>
+      <c r="A43" s="14">
+        <v>46184</v>
+      </c>
       <c r="B43" s="48">
         <v>39</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="18"/>
+      <c r="C43" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E43" s="19"/>
       <c r="F43" s="20"/>
       <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
+      <c r="H43" s="17">
+        <v>85</v>
+      </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
     </row>
     <row r="44" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="14"/>
+      <c r="A44" s="14">
+        <v>46197</v>
+      </c>
       <c r="B44" s="15">
         <v>40</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="18"/>
+      <c r="C44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="E44" s="19"/>
-      <c r="F44" s="20"/>
+      <c r="F44" s="20">
+        <v>22.19</v>
+      </c>
       <c r="G44" s="17"/>
       <c r="H44" s="17"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
     </row>
     <row r="45" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
+      <c r="A45" s="14">
+        <v>46198</v>
+      </c>
       <c r="B45" s="15">
         <v>41</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="18"/>
+      <c r="C45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E45" s="19"/>
       <c r="F45" s="20"/>
       <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
+      <c r="H45" s="17">
+        <v>33</v>
+      </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
     </row>
     <row r="46" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14">
+        <v>46199</v>
+      </c>
       <c r="B46" s="15">
         <v>42</v>
       </c>
+      <c r="C46" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E46" s="19"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17">
+        <v>61</v>
+      </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
     </row>
     <row r="47" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="14">
+        <v>46199</v>
+      </c>
       <c r="B47" s="15">
         <v>43</v>
       </c>
+      <c r="C47" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E47" s="19"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17">
+        <v>6</v>
+      </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
     </row>
     <row r="48" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="14"/>
+      <c r="A48" s="14">
+        <v>46199</v>
+      </c>
       <c r="B48" s="15">
         <v>44</v>
       </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="18"/>
+      <c r="C48" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E48" s="16"/>
-      <c r="F48" s="17"/>
+      <c r="F48" s="17">
+        <v>2</v>
+      </c>
       <c r="G48" s="17"/>
       <c r="H48" s="17"/>
       <c r="I48" s="2"/>
@@ -7077,7 +7156,7 @@
       </c>
       <c r="F111" s="26">
         <f>SUM(F3:F110)</f>
-        <v>5946.3800000000238</v>
+        <v>5970.5700000000234</v>
       </c>
       <c r="G111" s="26">
         <f>SUM(G3:G110)</f>
@@ -7085,7 +7164,7 @@
       </c>
       <c r="H111" s="26">
         <f>SUM(H3:H110)</f>
-        <v>6690.11</v>
+        <v>6875.11</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -7110,20 +7189,20 @@
       <c r="C113" s="23"/>
       <c r="D113" s="45"/>
       <c r="E113" s="26">
-        <f>E111+Ausgaben!F178</f>
+        <f>E111+Ausgaben!F179</f>
         <v>0</v>
       </c>
       <c r="F113" s="26">
-        <f>F111+Ausgaben!G178</f>
-        <v>1862.6400000000253</v>
+        <f>F111+Ausgaben!G179</f>
+        <v>1395.5900000000265</v>
       </c>
       <c r="G113" s="26">
-        <f>G111+Ausgaben!H178</f>
+        <f>G111+Ausgaben!H179</f>
         <v>2000.5</v>
       </c>
       <c r="H113" s="26">
-        <f>H111+Ausgaben!I178</f>
-        <v>3483.7</v>
+        <f>H111+Ausgaben!I179</f>
+        <v>3668.7</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
@@ -7148,7 +7227,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>7346.8400000000256</v>
+        <v>7064.7900000000263</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -7883,138 +7962,133 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C99:D100 H34:H40 H48:H110 G41:H45">
-    <cfRule type="cellIs" dxfId="55" priority="63" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97">
+    <cfRule type="cellIs" dxfId="53" priority="68" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97">
-    <cfRule type="cellIs" dxfId="54" priority="68" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D31 D41:D45 D48:D61">
-    <cfRule type="cellIs" dxfId="53" priority="6" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D20:D22 D31 D41:D61">
+    <cfRule type="cellIs" dxfId="52" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D89">
-    <cfRule type="cellIs" dxfId="52" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:F82">
-    <cfRule type="cellIs" dxfId="51" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:G81">
-    <cfRule type="cellIs" dxfId="50" priority="29" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101:G110">
-    <cfRule type="cellIs" dxfId="49" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="48" priority="88" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="88" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41:F41">
-    <cfRule type="cellIs" dxfId="47" priority="48" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E41:F42">
+    <cfRule type="cellIs" dxfId="46" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:G37 G38 E39:G40">
-    <cfRule type="cellIs" dxfId="46" priority="50" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="50" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:G49 G50:G51 E51:F51 F52:G52 G53:G58">
-    <cfRule type="cellIs" dxfId="45" priority="108" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="108" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E69:G71 G82:G83">
-    <cfRule type="cellIs" dxfId="44" priority="82" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="82" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E84:G89 D90:G98">
-    <cfRule type="cellIs" dxfId="43" priority="64" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:H3">
-    <cfRule type="cellIs" dxfId="42" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:H32">
-    <cfRule type="cellIs" dxfId="41" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:G25">
-    <cfRule type="cellIs" dxfId="40" priority="283" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="283" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:G60">
-    <cfRule type="cellIs" dxfId="39" priority="25" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72:G72">
-    <cfRule type="cellIs" dxfId="38" priority="80" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="80" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A93:C93">
-    <cfRule type="cellIs" dxfId="37" priority="196" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="196" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="cellIs" dxfId="36" priority="280" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="280" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
-    <cfRule type="cellIs" dxfId="35" priority="362" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="362" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H22">
-    <cfRule type="cellIs" dxfId="34" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:H31 G33:H33">
-    <cfRule type="cellIs" dxfId="33" priority="57" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="57" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10 B83">
-    <cfRule type="cellIs" dxfId="32" priority="210" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="210" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H27">
-    <cfRule type="cellIs" dxfId="31" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E42:F42">
-    <cfRule type="cellIs" dxfId="30" priority="1" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="H34:H40 C99:D100 H48:H110 G41:H47">
+    <cfRule type="cellIs" dxfId="29" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D28 D48:D110 D31:D45" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D28 D31:D110" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$J$1:$J$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -8035,7 +8109,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:IL244"/>
+  <dimension ref="A1:IL245"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="43" customWidth="1"/>
@@ -9984,14 +10058,22 @@
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="41"/>
-      <c r="B80" s="14"/>
+      <c r="B80" s="14">
+        <v>46184</v>
+      </c>
       <c r="C80" s="48">
         <v>76</v>
       </c>
-      <c r="D80" s="3"/>
-      <c r="E80" s="82"/>
+      <c r="D80" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E80" s="82" t="s">
+        <v>12</v>
+      </c>
       <c r="F80" s="19"/>
-      <c r="G80" s="20"/>
+      <c r="G80" s="20">
+        <v>-300</v>
+      </c>
       <c r="H80" s="20"/>
       <c r="I80" s="20"/>
       <c r="J80" s="4"/>
@@ -10000,14 +10082,22 @@
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="41"/>
-      <c r="B81" s="14"/>
+      <c r="B81" s="14">
+        <v>46184</v>
+      </c>
       <c r="C81" s="48">
         <v>77</v>
       </c>
-      <c r="D81" s="3"/>
-      <c r="E81" s="82"/>
+      <c r="D81" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E81" s="82" t="s">
+        <v>12</v>
+      </c>
       <c r="F81" s="19"/>
-      <c r="G81" s="20"/>
+      <c r="G81" s="20">
+        <v>-120</v>
+      </c>
       <c r="H81" s="20"/>
       <c r="I81" s="20"/>
       <c r="J81" s="4"/>
@@ -10016,14 +10106,22 @@
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="41"/>
-      <c r="B82" s="14"/>
+      <c r="B82" s="14">
+        <v>46184</v>
+      </c>
       <c r="C82" s="48">
         <v>78</v>
       </c>
-      <c r="D82" s="3"/>
-      <c r="E82" s="82"/>
+      <c r="D82" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F82" s="19"/>
-      <c r="G82" s="20"/>
+      <c r="G82" s="20">
+        <v>-9.3699999999999992</v>
+      </c>
       <c r="H82" s="20"/>
       <c r="I82" s="20"/>
       <c r="J82" s="4"/>
@@ -10032,14 +10130,22 @@
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="41"/>
-      <c r="B83" s="14"/>
+      <c r="B83" s="14">
+        <v>46188</v>
+      </c>
       <c r="C83" s="48">
         <v>79</v>
       </c>
-      <c r="D83" s="3"/>
-      <c r="E83" s="82"/>
+      <c r="D83" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F83" s="19"/>
-      <c r="G83" s="20"/>
+      <c r="G83" s="20">
+        <v>-12.95</v>
+      </c>
       <c r="H83" s="20"/>
       <c r="I83" s="20"/>
       <c r="J83" s="4"/>
@@ -10048,14 +10154,22 @@
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
-      <c r="B84" s="14"/>
+      <c r="B84" s="14">
+        <v>46197</v>
+      </c>
       <c r="C84" s="48">
         <v>80</v>
       </c>
-      <c r="D84" s="3"/>
-      <c r="E84" s="82"/>
+      <c r="D84" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F84" s="19"/>
-      <c r="G84" s="20"/>
+      <c r="G84" s="20">
+        <v>-20.99</v>
+      </c>
       <c r="H84" s="20"/>
       <c r="I84" s="20"/>
       <c r="J84" s="4"/>
@@ -10064,14 +10178,22 @@
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="41"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="48">
-        <v>81</v>
-      </c>
-      <c r="D85" s="3"/>
-      <c r="E85" s="82"/>
+      <c r="B85" s="14">
+        <v>46198</v>
+      </c>
+      <c r="C85" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E85" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F85" s="19"/>
-      <c r="G85" s="20"/>
+      <c r="G85" s="20">
+        <v>-4.99</v>
+      </c>
       <c r="H85" s="20"/>
       <c r="I85" s="20"/>
       <c r="J85" s="4"/>
@@ -10080,14 +10202,22 @@
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="41"/>
-      <c r="B86" s="14"/>
+      <c r="B86" s="14">
+        <v>46199</v>
+      </c>
       <c r="C86" s="48">
-        <v>82</v>
-      </c>
-      <c r="D86" s="81"/>
-      <c r="E86" s="82"/>
+        <v>81</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F86" s="19"/>
-      <c r="G86" s="20"/>
+      <c r="G86" s="20">
+        <v>-22.94</v>
+      </c>
       <c r="H86" s="20"/>
       <c r="I86" s="20"/>
       <c r="J86" s="4"/>
@@ -10098,7 +10228,7 @@
       <c r="A87" s="41"/>
       <c r="B87" s="14"/>
       <c r="C87" s="48">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D87" s="81"/>
       <c r="E87" s="82"/>
@@ -10114,7 +10244,7 @@
       <c r="A88" s="41"/>
       <c r="B88" s="14"/>
       <c r="C88" s="48">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D88" s="81"/>
       <c r="E88" s="82"/>
@@ -10130,9 +10260,9 @@
       <c r="A89" s="41"/>
       <c r="B89" s="14"/>
       <c r="C89" s="48">
-        <v>85</v>
-      </c>
-      <c r="D89" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="D89" s="81"/>
       <c r="E89" s="82"/>
       <c r="F89" s="19"/>
       <c r="G89" s="20"/>
@@ -10146,7 +10276,7 @@
       <c r="A90" s="41"/>
       <c r="B90" s="14"/>
       <c r="C90" s="48">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="82"/>
@@ -10162,7 +10292,7 @@
       <c r="A91" s="41"/>
       <c r="B91" s="14"/>
       <c r="C91" s="48">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="82"/>
@@ -10178,7 +10308,7 @@
       <c r="A92" s="41"/>
       <c r="B92" s="14"/>
       <c r="C92" s="48">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="82"/>
@@ -10194,7 +10324,7 @@
       <c r="A93" s="41"/>
       <c r="B93" s="14"/>
       <c r="C93" s="48">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="82"/>
@@ -10210,7 +10340,7 @@
       <c r="A94" s="41"/>
       <c r="B94" s="14"/>
       <c r="C94" s="48">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="82"/>
@@ -10226,9 +10356,9 @@
       <c r="A95" s="41"/>
       <c r="B95" s="14"/>
       <c r="C95" s="48">
-        <v>91</v>
-      </c>
-      <c r="D95" s="81"/>
+        <v>90</v>
+      </c>
+      <c r="D95" s="3"/>
       <c r="E95" s="82"/>
       <c r="F95" s="19"/>
       <c r="G95" s="20"/>
@@ -10242,9 +10372,9 @@
       <c r="A96" s="41"/>
       <c r="B96" s="14"/>
       <c r="C96" s="48">
-        <v>92</v>
-      </c>
-      <c r="D96" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="D96" s="81"/>
       <c r="E96" s="82"/>
       <c r="F96" s="19"/>
       <c r="G96" s="20"/>
@@ -10258,7 +10388,7 @@
       <c r="A97" s="41"/>
       <c r="B97" s="14"/>
       <c r="C97" s="48">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="82"/>
@@ -10274,11 +10404,11 @@
       <c r="A98" s="41"/>
       <c r="B98" s="14"/>
       <c r="C98" s="48">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="82"/>
-      <c r="F98" s="16"/>
+      <c r="F98" s="19"/>
       <c r="G98" s="20"/>
       <c r="H98" s="20"/>
       <c r="I98" s="20"/>
@@ -10290,7 +10420,7 @@
       <c r="A99" s="41"/>
       <c r="B99" s="14"/>
       <c r="C99" s="48">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="82"/>
@@ -10306,11 +10436,11 @@
       <c r="A100" s="41"/>
       <c r="B100" s="14"/>
       <c r="C100" s="48">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="82"/>
-      <c r="F100" s="19"/>
+      <c r="F100" s="16"/>
       <c r="G100" s="20"/>
       <c r="H100" s="20"/>
       <c r="I100" s="20"/>
@@ -10322,7 +10452,7 @@
       <c r="A101" s="41"/>
       <c r="B101" s="14"/>
       <c r="C101" s="48">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="82"/>
@@ -10338,7 +10468,7 @@
       <c r="A102" s="41"/>
       <c r="B102" s="14"/>
       <c r="C102" s="48">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="82"/>
@@ -10349,16 +10479,14 @@
       <c r="J102" s="4"/>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
-      <c r="IK102"/>
-      <c r="IL102"/>
     </row>
     <row r="103" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="41"/>
       <c r="B103" s="14"/>
       <c r="C103" s="48">
-        <v>99</v>
-      </c>
-      <c r="D103" s="81"/>
+        <v>98</v>
+      </c>
+      <c r="D103" s="3"/>
       <c r="E103" s="82"/>
       <c r="F103" s="19"/>
       <c r="G103" s="20"/>
@@ -10367,14 +10495,16 @@
       <c r="J103" s="4"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
+      <c r="IK103"/>
+      <c r="IL103"/>
     </row>
     <row r="104" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="41"/>
       <c r="B104" s="14"/>
       <c r="C104" s="48">
-        <v>100</v>
-      </c>
-      <c r="D104" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="D104" s="81"/>
       <c r="E104" s="82"/>
       <c r="F104" s="19"/>
       <c r="G104" s="20"/>
@@ -10388,7 +10518,7 @@
       <c r="A105" s="41"/>
       <c r="B105" s="14"/>
       <c r="C105" s="48">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="82"/>
@@ -10404,9 +10534,9 @@
       <c r="A106" s="41"/>
       <c r="B106" s="14"/>
       <c r="C106" s="48">
-        <v>102</v>
-      </c>
-      <c r="D106" s="81"/>
+        <v>101</v>
+      </c>
+      <c r="D106" s="3"/>
       <c r="E106" s="82"/>
       <c r="F106" s="19"/>
       <c r="G106" s="20"/>
@@ -10420,9 +10550,9 @@
       <c r="A107" s="41"/>
       <c r="B107" s="14"/>
       <c r="C107" s="48">
-        <v>103</v>
-      </c>
-      <c r="D107" s="3"/>
+        <v>102</v>
+      </c>
+      <c r="D107" s="81"/>
       <c r="E107" s="82"/>
       <c r="F107" s="19"/>
       <c r="G107" s="20"/>
@@ -10436,7 +10566,7 @@
       <c r="A108" s="41"/>
       <c r="B108" s="14"/>
       <c r="C108" s="48">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="82"/>
@@ -10452,7 +10582,7 @@
       <c r="A109" s="41"/>
       <c r="B109" s="14"/>
       <c r="C109" s="48">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="82"/>
@@ -10468,7 +10598,7 @@
       <c r="A110" s="41"/>
       <c r="B110" s="14"/>
       <c r="C110" s="48">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="82"/>
@@ -10484,7 +10614,7 @@
       <c r="A111" s="41"/>
       <c r="B111" s="14"/>
       <c r="C111" s="48">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="82"/>
@@ -10500,9 +10630,9 @@
       <c r="A112" s="41"/>
       <c r="B112" s="14"/>
       <c r="C112" s="48">
-        <v>108</v>
-      </c>
-      <c r="D112" s="81"/>
+        <v>107</v>
+      </c>
+      <c r="D112" s="3"/>
       <c r="E112" s="82"/>
       <c r="F112" s="19"/>
       <c r="G112" s="20"/>
@@ -10516,9 +10646,9 @@
       <c r="A113" s="41"/>
       <c r="B113" s="14"/>
       <c r="C113" s="48">
-        <v>109</v>
-      </c>
-      <c r="D113" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="D113" s="81"/>
       <c r="E113" s="82"/>
       <c r="F113" s="19"/>
       <c r="G113" s="20"/>
@@ -10532,7 +10662,7 @@
       <c r="A114" s="41"/>
       <c r="B114" s="14"/>
       <c r="C114" s="48">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="82"/>
@@ -10548,7 +10678,7 @@
       <c r="A115" s="41"/>
       <c r="B115" s="14"/>
       <c r="C115" s="48">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="82"/>
@@ -10564,11 +10694,11 @@
       <c r="A116" s="41"/>
       <c r="B116" s="14"/>
       <c r="C116" s="48">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="82"/>
-      <c r="F116" s="16"/>
+      <c r="F116" s="19"/>
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
       <c r="I116" s="20"/>
@@ -10580,11 +10710,11 @@
       <c r="A117" s="41"/>
       <c r="B117" s="14"/>
       <c r="C117" s="48">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D117" s="3"/>
-      <c r="E117" s="21"/>
-      <c r="F117" s="19"/>
+      <c r="E117" s="82"/>
+      <c r="F117" s="16"/>
       <c r="G117" s="20"/>
       <c r="H117" s="20"/>
       <c r="I117" s="20"/>
@@ -10596,10 +10726,10 @@
       <c r="A118" s="41"/>
       <c r="B118" s="14"/>
       <c r="C118" s="48">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D118" s="3"/>
-      <c r="E118" s="82"/>
+      <c r="E118" s="21"/>
       <c r="F118" s="19"/>
       <c r="G118" s="20"/>
       <c r="H118" s="20"/>
@@ -10612,7 +10742,7 @@
       <c r="A119" s="41"/>
       <c r="B119" s="14"/>
       <c r="C119" s="48">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="82"/>
@@ -10628,7 +10758,7 @@
       <c r="A120" s="41"/>
       <c r="B120" s="14"/>
       <c r="C120" s="48">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="82"/>
@@ -10644,7 +10774,7 @@
       <c r="A121" s="41"/>
       <c r="B121" s="14"/>
       <c r="C121" s="48">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="82"/>
@@ -10660,7 +10790,7 @@
       <c r="A122" s="41"/>
       <c r="B122" s="14"/>
       <c r="C122" s="48">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="82"/>
@@ -10676,7 +10806,7 @@
       <c r="A123" s="41"/>
       <c r="B123" s="14"/>
       <c r="C123" s="48">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="82"/>
@@ -10692,10 +10822,10 @@
       <c r="A124" s="41"/>
       <c r="B124" s="14"/>
       <c r="C124" s="48">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D124" s="3"/>
-      <c r="E124" s="2"/>
+      <c r="E124" s="82"/>
       <c r="F124" s="19"/>
       <c r="G124" s="20"/>
       <c r="H124" s="20"/>
@@ -10708,10 +10838,10 @@
       <c r="A125" s="41"/>
       <c r="B125" s="14"/>
       <c r="C125" s="48">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D125" s="3"/>
-      <c r="E125" s="82"/>
+      <c r="E125" s="2"/>
       <c r="F125" s="19"/>
       <c r="G125" s="20"/>
       <c r="H125" s="20"/>
@@ -10724,9 +10854,9 @@
       <c r="A126" s="41"/>
       <c r="B126" s="14"/>
       <c r="C126" s="48">
-        <v>122</v>
-      </c>
-      <c r="D126" s="81"/>
+        <v>121</v>
+      </c>
+      <c r="D126" s="3"/>
       <c r="E126" s="82"/>
       <c r="F126" s="19"/>
       <c r="G126" s="20"/>
@@ -10740,9 +10870,9 @@
       <c r="A127" s="41"/>
       <c r="B127" s="14"/>
       <c r="C127" s="48">
-        <v>123</v>
-      </c>
-      <c r="D127" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="D127" s="81"/>
       <c r="E127" s="82"/>
       <c r="F127" s="19"/>
       <c r="G127" s="20"/>
@@ -10756,7 +10886,7 @@
       <c r="A128" s="41"/>
       <c r="B128" s="14"/>
       <c r="C128" s="48">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="82"/>
@@ -10772,7 +10902,7 @@
       <c r="A129" s="41"/>
       <c r="B129" s="14"/>
       <c r="C129" s="48">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="82"/>
@@ -10788,7 +10918,7 @@
       <c r="A130" s="41"/>
       <c r="B130" s="14"/>
       <c r="C130" s="48">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="82"/>
@@ -10804,9 +10934,9 @@
       <c r="A131" s="41"/>
       <c r="B131" s="14"/>
       <c r="C131" s="48">
-        <v>127</v>
-      </c>
-      <c r="D131" s="81"/>
+        <v>126</v>
+      </c>
+      <c r="D131" s="3"/>
       <c r="E131" s="82"/>
       <c r="F131" s="19"/>
       <c r="G131" s="20"/>
@@ -10820,10 +10950,10 @@
       <c r="A132" s="41"/>
       <c r="B132" s="14"/>
       <c r="C132" s="48">
-        <v>128</v>
-      </c>
-      <c r="D132" s="37"/>
-      <c r="E132" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="D132" s="81"/>
+      <c r="E132" s="82"/>
       <c r="F132" s="19"/>
       <c r="G132" s="20"/>
       <c r="H132" s="20"/>
@@ -10836,10 +10966,10 @@
       <c r="A133" s="41"/>
       <c r="B133" s="14"/>
       <c r="C133" s="48">
-        <v>129</v>
-      </c>
-      <c r="D133" s="3"/>
-      <c r="E133" s="82"/>
+        <v>128</v>
+      </c>
+      <c r="D133" s="37"/>
+      <c r="E133" s="2"/>
       <c r="F133" s="19"/>
       <c r="G133" s="20"/>
       <c r="H133" s="20"/>
@@ -10852,10 +10982,10 @@
       <c r="A134" s="41"/>
       <c r="B134" s="14"/>
       <c r="C134" s="48">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D134" s="3"/>
-      <c r="E134" s="21"/>
+      <c r="E134" s="82"/>
       <c r="F134" s="19"/>
       <c r="G134" s="20"/>
       <c r="H134" s="20"/>
@@ -10868,10 +10998,10 @@
       <c r="A135" s="41"/>
       <c r="B135" s="14"/>
       <c r="C135" s="48">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D135" s="3"/>
-      <c r="E135" s="82"/>
+      <c r="E135" s="21"/>
       <c r="F135" s="19"/>
       <c r="G135" s="20"/>
       <c r="H135" s="20"/>
@@ -10884,10 +11014,10 @@
       <c r="A136" s="41"/>
       <c r="B136" s="14"/>
       <c r="C136" s="48">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D136" s="3"/>
-      <c r="E136" s="21"/>
+      <c r="E136" s="82"/>
       <c r="F136" s="19"/>
       <c r="G136" s="20"/>
       <c r="H136" s="20"/>
@@ -10900,7 +11030,7 @@
       <c r="A137" s="41"/>
       <c r="B137" s="14"/>
       <c r="C137" s="48">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="21"/>
@@ -10916,10 +11046,10 @@
       <c r="A138" s="41"/>
       <c r="B138" s="14"/>
       <c r="C138" s="48">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D138" s="3"/>
-      <c r="E138" s="82"/>
+      <c r="E138" s="21"/>
       <c r="F138" s="19"/>
       <c r="G138" s="20"/>
       <c r="H138" s="20"/>
@@ -10932,10 +11062,10 @@
       <c r="A139" s="41"/>
       <c r="B139" s="14"/>
       <c r="C139" s="48">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D139" s="3"/>
-      <c r="E139" s="21"/>
+      <c r="E139" s="82"/>
       <c r="F139" s="19"/>
       <c r="G139" s="20"/>
       <c r="H139" s="20"/>
@@ -10948,10 +11078,10 @@
       <c r="A140" s="41"/>
       <c r="B140" s="14"/>
       <c r="C140" s="48">
-        <v>136</v>
-      </c>
-      <c r="D140" s="81"/>
-      <c r="E140" s="82"/>
+        <v>135</v>
+      </c>
+      <c r="D140" s="3"/>
+      <c r="E140" s="21"/>
       <c r="F140" s="19"/>
       <c r="G140" s="20"/>
       <c r="H140" s="20"/>
@@ -10964,7 +11094,7 @@
       <c r="A141" s="41"/>
       <c r="B141" s="14"/>
       <c r="C141" s="48">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D141" s="81"/>
       <c r="E141" s="82"/>
@@ -10980,7 +11110,7 @@
       <c r="A142" s="41"/>
       <c r="B142" s="14"/>
       <c r="C142" s="48">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D142" s="81"/>
       <c r="E142" s="82"/>
@@ -10996,9 +11126,9 @@
       <c r="A143" s="41"/>
       <c r="B143" s="14"/>
       <c r="C143" s="48">
-        <v>139</v>
-      </c>
-      <c r="D143" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="D143" s="81"/>
       <c r="E143" s="82"/>
       <c r="F143" s="19"/>
       <c r="G143" s="20"/>
@@ -11012,7 +11142,7 @@
       <c r="A144" s="41"/>
       <c r="B144" s="14"/>
       <c r="C144" s="48">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="82"/>
@@ -11028,10 +11158,10 @@
       <c r="A145" s="41"/>
       <c r="B145" s="14"/>
       <c r="C145" s="48">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D145" s="3"/>
-      <c r="E145" s="2"/>
+      <c r="E145" s="82"/>
       <c r="F145" s="19"/>
       <c r="G145" s="20"/>
       <c r="H145" s="20"/>
@@ -11047,7 +11177,7 @@
         <v>141</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="82"/>
+      <c r="E146" s="2"/>
       <c r="F146" s="19"/>
       <c r="G146" s="20"/>
       <c r="H146" s="20"/>
@@ -11060,7 +11190,7 @@
       <c r="A147" s="41"/>
       <c r="B147" s="14"/>
       <c r="C147" s="48">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="82"/>
@@ -11076,40 +11206,40 @@
       <c r="A148" s="41"/>
       <c r="B148" s="14"/>
       <c r="C148" s="48">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D148" s="3"/>
-      <c r="E148" s="21"/>
+      <c r="E148" s="82"/>
       <c r="F148" s="19"/>
       <c r="G148" s="20"/>
       <c r="H148" s="20"/>
       <c r="I148" s="20"/>
       <c r="J148" s="4"/>
       <c r="K148" s="2"/>
+      <c r="L148" s="2"/>
     </row>
     <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="41"/>
       <c r="B149" s="14"/>
       <c r="C149" s="48">
-        <v>144</v>
-      </c>
-      <c r="D149" s="37"/>
-      <c r="E149" s="82"/>
+        <v>143</v>
+      </c>
+      <c r="D149" s="3"/>
+      <c r="E149" s="21"/>
       <c r="F149" s="19"/>
       <c r="G149" s="20"/>
       <c r="H149" s="20"/>
       <c r="I149" s="20"/>
       <c r="J149" s="4"/>
       <c r="K149" s="2"/>
-      <c r="L149" s="2"/>
     </row>
     <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="41"/>
       <c r="B150" s="14"/>
       <c r="C150" s="48">
-        <v>145</v>
-      </c>
-      <c r="D150" s="81"/>
+        <v>144</v>
+      </c>
+      <c r="D150" s="37"/>
       <c r="E150" s="82"/>
       <c r="F150" s="19"/>
       <c r="G150" s="20"/>
@@ -11123,9 +11253,9 @@
       <c r="A151" s="41"/>
       <c r="B151" s="14"/>
       <c r="C151" s="48">
-        <v>146</v>
-      </c>
-      <c r="D151" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="D151" s="81"/>
       <c r="E151" s="82"/>
       <c r="F151" s="19"/>
       <c r="G151" s="20"/>
@@ -11139,10 +11269,10 @@
       <c r="A152" s="41"/>
       <c r="B152" s="14"/>
       <c r="C152" s="48">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D152" s="3"/>
-      <c r="E152" s="21"/>
+      <c r="E152" s="82"/>
       <c r="F152" s="19"/>
       <c r="G152" s="20"/>
       <c r="H152" s="20"/>
@@ -11155,9 +11285,9 @@
       <c r="A153" s="41"/>
       <c r="B153" s="14"/>
       <c r="C153" s="48">
-        <v>148</v>
-      </c>
-      <c r="D153" s="37"/>
+        <v>147</v>
+      </c>
+      <c r="D153" s="3"/>
       <c r="E153" s="21"/>
       <c r="F153" s="19"/>
       <c r="G153" s="20"/>
@@ -11187,10 +11317,10 @@
       <c r="A155" s="41"/>
       <c r="B155" s="14"/>
       <c r="C155" s="48">
-        <v>149</v>
-      </c>
-      <c r="D155" s="3"/>
-      <c r="E155" s="82"/>
+        <v>148</v>
+      </c>
+      <c r="D155" s="37"/>
+      <c r="E155" s="21"/>
       <c r="F155" s="19"/>
       <c r="G155" s="20"/>
       <c r="H155" s="20"/>
@@ -11203,9 +11333,9 @@
       <c r="A156" s="41"/>
       <c r="B156" s="14"/>
       <c r="C156" s="48">
-        <v>149.69999999999999</v>
-      </c>
-      <c r="D156" s="81"/>
+        <v>149</v>
+      </c>
+      <c r="D156" s="3"/>
       <c r="E156" s="82"/>
       <c r="F156" s="19"/>
       <c r="G156" s="20"/>
@@ -11219,7 +11349,7 @@
       <c r="A157" s="41"/>
       <c r="B157" s="14"/>
       <c r="C157" s="48">
-        <v>151</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="D157" s="81"/>
       <c r="E157" s="82"/>
@@ -11235,10 +11365,10 @@
       <c r="A158" s="41"/>
       <c r="B158" s="14"/>
       <c r="C158" s="48">
-        <v>152</v>
-      </c>
-      <c r="D158" s="37"/>
-      <c r="E158" s="21"/>
+        <v>151</v>
+      </c>
+      <c r="D158" s="81"/>
+      <c r="E158" s="82"/>
       <c r="F158" s="19"/>
       <c r="G158" s="20"/>
       <c r="H158" s="20"/>
@@ -11251,7 +11381,7 @@
       <c r="A159" s="41"/>
       <c r="B159" s="14"/>
       <c r="C159" s="48">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D159" s="37"/>
       <c r="E159" s="21"/>
@@ -11267,7 +11397,7 @@
       <c r="A160" s="41"/>
       <c r="B160" s="14"/>
       <c r="C160" s="48">
-        <v>154.03</v>
+        <v>153</v>
       </c>
       <c r="D160" s="37"/>
       <c r="E160" s="21"/>
@@ -11283,7 +11413,7 @@
       <c r="A161" s="41"/>
       <c r="B161" s="14"/>
       <c r="C161" s="48">
-        <v>155.06</v>
+        <v>154.03</v>
       </c>
       <c r="D161" s="37"/>
       <c r="E161" s="21"/>
@@ -11299,7 +11429,7 @@
       <c r="A162" s="41"/>
       <c r="B162" s="14"/>
       <c r="C162" s="48">
-        <v>156.09</v>
+        <v>155.06</v>
       </c>
       <c r="D162" s="37"/>
       <c r="E162" s="21"/>
@@ -11315,7 +11445,7 @@
       <c r="A163" s="41"/>
       <c r="B163" s="14"/>
       <c r="C163" s="48">
-        <v>157.12</v>
+        <v>156.09</v>
       </c>
       <c r="D163" s="37"/>
       <c r="E163" s="21"/>
@@ -11331,10 +11461,10 @@
       <c r="A164" s="41"/>
       <c r="B164" s="14"/>
       <c r="C164" s="48">
-        <v>158.15</v>
+        <v>157.12</v>
       </c>
       <c r="D164" s="37"/>
-      <c r="E164" s="18"/>
+      <c r="E164" s="21"/>
       <c r="F164" s="19"/>
       <c r="G164" s="20"/>
       <c r="H164" s="20"/>
@@ -11347,10 +11477,10 @@
       <c r="A165" s="41"/>
       <c r="B165" s="14"/>
       <c r="C165" s="48">
-        <v>159.18</v>
+        <v>158.15</v>
       </c>
       <c r="D165" s="37"/>
-      <c r="E165" s="21"/>
+      <c r="E165" s="18"/>
       <c r="F165" s="19"/>
       <c r="G165" s="20"/>
       <c r="H165" s="20"/>
@@ -11363,11 +11493,11 @@
       <c r="A166" s="41"/>
       <c r="B166" s="14"/>
       <c r="C166" s="48">
-        <v>160.21</v>
+        <v>159.18</v>
       </c>
       <c r="D166" s="37"/>
       <c r="E166" s="21"/>
-      <c r="F166" s="20"/>
+      <c r="F166" s="19"/>
       <c r="G166" s="20"/>
       <c r="H166" s="20"/>
       <c r="I166" s="20"/>
@@ -11379,11 +11509,11 @@
       <c r="A167" s="41"/>
       <c r="B167" s="14"/>
       <c r="C167" s="48">
-        <v>161.24</v>
+        <v>160.21</v>
       </c>
       <c r="D167" s="37"/>
       <c r="E167" s="21"/>
-      <c r="F167" s="19"/>
+      <c r="F167" s="20"/>
       <c r="G167" s="20"/>
       <c r="H167" s="20"/>
       <c r="I167" s="20"/>
@@ -11395,10 +11525,10 @@
       <c r="A168" s="41"/>
       <c r="B168" s="14"/>
       <c r="C168" s="48">
-        <v>162.27000000000001</v>
-      </c>
-      <c r="D168" s="3"/>
-      <c r="E168" s="82"/>
+        <v>161.24</v>
+      </c>
+      <c r="D168" s="37"/>
+      <c r="E168" s="21"/>
       <c r="F168" s="19"/>
       <c r="G168" s="20"/>
       <c r="H168" s="20"/>
@@ -11411,10 +11541,10 @@
       <c r="A169" s="41"/>
       <c r="B169" s="14"/>
       <c r="C169" s="48">
-        <v>163.30000000000001</v>
-      </c>
-      <c r="D169" s="37"/>
-      <c r="E169" s="21"/>
+        <v>162.27000000000001</v>
+      </c>
+      <c r="D169" s="3"/>
+      <c r="E169" s="82"/>
       <c r="F169" s="19"/>
       <c r="G169" s="20"/>
       <c r="H169" s="20"/>
@@ -11427,10 +11557,10 @@
       <c r="A170" s="41"/>
       <c r="B170" s="14"/>
       <c r="C170" s="48">
-        <v>164.33</v>
+        <v>163.30000000000001</v>
       </c>
       <c r="D170" s="37"/>
-      <c r="E170" s="18"/>
+      <c r="E170" s="21"/>
       <c r="F170" s="19"/>
       <c r="G170" s="20"/>
       <c r="H170" s="20"/>
@@ -11443,10 +11573,10 @@
       <c r="A171" s="41"/>
       <c r="B171" s="14"/>
       <c r="C171" s="48">
-        <v>165.36</v>
+        <v>164.33</v>
       </c>
       <c r="D171" s="37"/>
-      <c r="E171" s="21"/>
+      <c r="E171" s="18"/>
       <c r="F171" s="19"/>
       <c r="G171" s="20"/>
       <c r="H171" s="20"/>
@@ -11459,10 +11589,10 @@
       <c r="A172" s="41"/>
       <c r="B172" s="14"/>
       <c r="C172" s="48">
-        <v>166.39</v>
-      </c>
-      <c r="D172" s="15"/>
-      <c r="E172" s="18"/>
+        <v>165.36</v>
+      </c>
+      <c r="D172" s="37"/>
+      <c r="E172" s="21"/>
       <c r="F172" s="19"/>
       <c r="G172" s="20"/>
       <c r="H172" s="20"/>
@@ -11475,7 +11605,7 @@
       <c r="A173" s="41"/>
       <c r="B173" s="14"/>
       <c r="C173" s="48">
-        <v>167.42</v>
+        <v>166.39</v>
       </c>
       <c r="D173" s="15"/>
       <c r="E173" s="18"/>
@@ -11491,7 +11621,7 @@
       <c r="A174" s="41"/>
       <c r="B174" s="14"/>
       <c r="C174" s="48">
-        <v>168.45</v>
+        <v>167.42</v>
       </c>
       <c r="D174" s="15"/>
       <c r="E174" s="18"/>
@@ -11499,7 +11629,7 @@
       <c r="G174" s="20"/>
       <c r="H174" s="20"/>
       <c r="I174" s="20"/>
-      <c r="J174" s="44"/>
+      <c r="J174" s="4"/>
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
     </row>
@@ -11507,7 +11637,7 @@
       <c r="A175" s="41"/>
       <c r="B175" s="14"/>
       <c r="C175" s="48">
-        <v>169.48</v>
+        <v>168.45</v>
       </c>
       <c r="D175" s="15"/>
       <c r="E175" s="18"/>
@@ -11523,7 +11653,7 @@
       <c r="A176" s="41"/>
       <c r="B176" s="14"/>
       <c r="C176" s="48">
-        <v>170.51</v>
+        <v>169.48</v>
       </c>
       <c r="D176" s="15"/>
       <c r="E176" s="18"/>
@@ -11538,8 +11668,10 @@
     <row r="177" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="41"/>
       <c r="B177" s="14"/>
-      <c r="C177" s="48"/>
-      <c r="D177" s="37"/>
+      <c r="C177" s="48">
+        <v>170.51</v>
+      </c>
+      <c r="D177" s="15"/>
       <c r="E177" s="18"/>
       <c r="F177" s="19"/>
       <c r="G177" s="20"/>
@@ -11548,46 +11680,46 @@
       <c r="J177" s="44"/>
       <c r="K177" s="2"/>
       <c r="L177" s="2"/>
-      <c r="IL177"/>
     </row>
     <row r="178" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="42"/>
-      <c r="B178" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C178" s="49"/>
-      <c r="D178" s="29"/>
-      <c r="E178" s="30"/>
-      <c r="F178" s="31">
-        <f>SUM(F3:F177)</f>
-        <v>0</v>
-      </c>
-      <c r="G178" s="32">
-        <f>SUM(G3:G177)</f>
-        <v>-4083.7399999999984</v>
-      </c>
-      <c r="H178" s="32">
-        <f>SUM(H3:H177)</f>
-        <v>0</v>
-      </c>
-      <c r="I178" s="32">
-        <f>SUM(I3:I177)</f>
-        <v>-3206.41</v>
-      </c>
-      <c r="J178" s="2"/>
+      <c r="A178" s="41"/>
+      <c r="B178" s="14"/>
+      <c r="C178" s="48"/>
+      <c r="D178" s="37"/>
+      <c r="E178" s="18"/>
+      <c r="F178" s="19"/>
+      <c r="G178" s="20"/>
+      <c r="H178" s="20"/>
+      <c r="I178" s="20"/>
+      <c r="J178" s="44"/>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
+      <c r="IL178"/>
     </row>
     <row r="179" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="42"/>
-      <c r="B179" s="17"/>
-      <c r="C179" s="17"/>
-      <c r="D179" s="17"/>
-      <c r="E179" s="17"/>
-      <c r="F179" s="17"/>
-      <c r="G179" s="17"/>
-      <c r="H179" s="17"/>
-      <c r="I179" s="17"/>
+      <c r="B179" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179" s="49"/>
+      <c r="D179" s="29"/>
+      <c r="E179" s="30"/>
+      <c r="F179" s="31">
+        <f>SUM(F3:F178)</f>
+        <v>0</v>
+      </c>
+      <c r="G179" s="32">
+        <f>SUM(G3:G178)</f>
+        <v>-4574.9799999999968</v>
+      </c>
+      <c r="H179" s="32">
+        <f>SUM(H3:H178)</f>
+        <v>0</v>
+      </c>
+      <c r="I179" s="32">
+        <f>SUM(I3:I178)</f>
+        <v>-3206.41</v>
+      </c>
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
@@ -12446,7 +12578,7 @@
       <c r="K240" s="2"/>
       <c r="L240" s="2"/>
     </row>
-    <row r="241" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="42"/>
       <c r="B241" s="17"/>
       <c r="C241" s="17"/>
@@ -12458,8 +12590,9 @@
       <c r="I241" s="17"/>
       <c r="J241" s="2"/>
       <c r="K241" s="2"/>
-    </row>
-    <row r="242" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L241" s="2"/>
+    </row>
+    <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="42"/>
       <c r="B242" s="17"/>
       <c r="C242" s="17"/>
@@ -12470,173 +12603,181 @@
       <c r="H242" s="17"/>
       <c r="I242" s="17"/>
       <c r="J242" s="2"/>
-    </row>
-    <row r="243" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K242" s="2"/>
+    </row>
+    <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="42"/>
       <c r="B243" s="17"/>
       <c r="C243" s="17"/>
+      <c r="D243" s="17"/>
+      <c r="E243" s="17"/>
+      <c r="F243" s="17"/>
+      <c r="G243" s="17"/>
+      <c r="H243" s="17"/>
       <c r="I243" s="17"/>
-    </row>
-    <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J243" s="2"/>
+    </row>
+    <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B244" s="17"/>
+      <c r="C244" s="17"/>
       <c r="I244" s="17"/>
     </row>
+    <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B245" s="17"/>
+      <c r="I245" s="17"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:J173" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="B2:J174" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A242 E33 E80:E123 E133:E144">
-    <cfRule type="cellIs" dxfId="29" priority="494" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A3:A243 E33 E134:E145">
+    <cfRule type="cellIs" dxfId="28" priority="495" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B129:B142">
-    <cfRule type="cellIs" dxfId="28" priority="477" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="B130:B143">
+    <cfRule type="cellIs" dxfId="27" priority="478" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B156:B244">
-    <cfRule type="cellIs" dxfId="27" priority="34" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C155 C157 C159 C161 C163 C165 C167 C173 C175">
+  <conditionalFormatting sqref="B157:B245">
     <cfRule type="cellIs" dxfId="26" priority="35" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C177:C243 J179 I179:I244">
-    <cfRule type="cellIs" dxfId="25" priority="724" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C156 C158 C160 C162 C164 C166 C168 C174 C176">
+    <cfRule type="cellIs" dxfId="25" priority="36" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D132">
-    <cfRule type="cellIs" dxfId="24" priority="492" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C178:C244 J180 I180:I245">
+    <cfRule type="cellIs" dxfId="24" priority="725" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D149">
-    <cfRule type="cellIs" dxfId="23" priority="79" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D133">
+    <cfRule type="cellIs" dxfId="23" priority="493" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D153:D154">
-    <cfRule type="cellIs" dxfId="22" priority="463" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D150">
+    <cfRule type="cellIs" dxfId="22" priority="80" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D158:D163">
-    <cfRule type="cellIs" dxfId="21" priority="20" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D154:D155">
+    <cfRule type="cellIs" dxfId="21" priority="464" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D164:E165 D166:D167 C169:D169 D170:E170 C171:D171">
-    <cfRule type="cellIs" dxfId="20" priority="27" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D159:D164">
+    <cfRule type="cellIs" dxfId="20" priority="21" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D177:E179">
-    <cfRule type="cellIs" dxfId="19" priority="29" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D165:E166 D167:D168 C170:D170 D171:E171 C172:D172">
+    <cfRule type="cellIs" dxfId="19" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D179:H242">
-    <cfRule type="cellIs" dxfId="18" priority="676" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D178:E180">
+    <cfRule type="cellIs" dxfId="18" priority="30" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E125:E131 E146:E163">
-    <cfRule type="cellIs" dxfId="17" priority="15" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D180:H243">
+    <cfRule type="cellIs" dxfId="17" priority="677" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E126:E132 E147:E164">
+    <cfRule type="cellIs" dxfId="16" priority="16" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="16" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="14" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58:E59">
-    <cfRule type="cellIs" dxfId="13" priority="9" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61">
-    <cfRule type="cellIs" dxfId="12" priority="8" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="9" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E64">
-    <cfRule type="cellIs" dxfId="11" priority="7" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E66:E68">
-    <cfRule type="cellIs" dxfId="10" priority="6" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72">
-    <cfRule type="cellIs" dxfId="9" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E166:E169">
-    <cfRule type="cellIs" dxfId="8" priority="17" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E76:E81 E87:E124">
+    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E171:E176">
-    <cfRule type="cellIs" dxfId="7" priority="16" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E167:E170">
+    <cfRule type="cellIs" dxfId="6" priority="18" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E172:E177">
+    <cfRule type="cellIs" dxfId="5" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="6" priority="14" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="15" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F98:F99">
-    <cfRule type="cellIs" dxfId="5" priority="137" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F116">
-    <cfRule type="cellIs" dxfId="4" priority="21" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E76">
+  <conditionalFormatting sqref="F77">
     <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E77">
-    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F99:F100">
+    <cfRule type="cellIs" dxfId="2" priority="138" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F77">
-    <cfRule type="cellIs" dxfId="1" priority="3" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F117">
+    <cfRule type="cellIs" dxfId="1" priority="22" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E78:E79">
+  <conditionalFormatting sqref="E85">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E146:E177 E125:E131 E133:E144 E58:E59 E72 E61 E64 E66:E68 E76:E123" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E147:E178 E126:E132 E134:E145 E58:E59 E72 E61 E64 E66:E68 E76:E81 E87:E124 E85" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$L$1:$L$19</formula1>
     </dataValidation>
   </dataValidations>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBC7371-602D-47C3-A385-A33FB7D1C762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55E1962-3B49-4FC7-88A8-E0A0856C2E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Einnahmen" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="131">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -409,6 +409,24 @@
   </si>
   <si>
     <t>80a</t>
+  </si>
+  <si>
+    <t>SPD 24.6. Miete</t>
+  </si>
+  <si>
+    <t>Busreise</t>
+  </si>
+  <si>
+    <t>D.Müller Spende</t>
+  </si>
+  <si>
+    <t>Getränle Heißwolf</t>
+  </si>
+  <si>
+    <t>A.Haefner Beitrag Jul-Dez</t>
+  </si>
+  <si>
+    <t>Shirts&amp;Sonnenschirm&amp;Sonstiges</t>
   </si>
 </sst>
 </file>
@@ -957,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1072,6 +1090,7 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1084,7 +1103,12 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="61">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -3925,17 +3949,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="56">
+    <format dxfId="57">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4039,17 +4063,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="59">
+    <format dxfId="60">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -5190,16 +5214,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3" t="s">
         <v>0</v>
@@ -6281,71 +6305,112 @@
       <c r="J48" s="2"/>
     </row>
     <row r="49" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="84">
+        <v>46202</v>
+      </c>
       <c r="B49" s="15">
         <v>45</v>
       </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="18"/>
+      <c r="C49" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E49" s="16"/>
       <c r="F49" s="17"/>
       <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
+      <c r="H49" s="17">
+        <v>20</v>
+      </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
     </row>
     <row r="50" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="14"/>
+      <c r="A50" s="14">
+        <v>46203</v>
+      </c>
       <c r="B50" s="15">
         <v>46</v>
       </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="18"/>
+      <c r="C50" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>13</v>
+      </c>
       <c r="E50" s="19"/>
       <c r="F50" s="20"/>
       <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
+      <c r="H50" s="17">
+        <v>110</v>
+      </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
     </row>
     <row r="51" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="14"/>
+      <c r="A51" s="14">
+        <v>46203</v>
+      </c>
       <c r="B51" s="15">
         <v>47</v>
       </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="18"/>
+      <c r="C51" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>12</v>
+      </c>
       <c r="E51" s="16"/>
       <c r="F51" s="17"/>
       <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
+      <c r="H51" s="17">
+        <v>100</v>
+      </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
     </row>
     <row r="52" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="14"/>
+      <c r="A52" s="14">
+        <v>46203</v>
+      </c>
       <c r="B52" s="15">
         <v>48</v>
       </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="18"/>
+      <c r="C52" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E52" s="19"/>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
+      <c r="H52" s="17">
+        <v>20</v>
+      </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
     </row>
     <row r="53" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="14"/>
+      <c r="A53" s="14">
+        <v>46206</v>
+      </c>
       <c r="B53" s="15">
         <v>49</v>
       </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="18"/>
+      <c r="C53" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="E53" s="19"/>
       <c r="F53" s="20"/>
       <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
+      <c r="H53" s="17">
+        <v>15</v>
+      </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
     </row>
@@ -7164,7 +7229,7 @@
       </c>
       <c r="H111" s="26">
         <f>SUM(H3:H110)</f>
-        <v>6875.11</v>
+        <v>7140.11</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -7194,7 +7259,7 @@
       </c>
       <c r="F113" s="26">
         <f>F111+Ausgaben!G179</f>
-        <v>1395.5900000000265</v>
+        <v>1219.6700000000274</v>
       </c>
       <c r="G113" s="26">
         <f>G111+Ausgaben!H179</f>
@@ -7202,7 +7267,7 @@
       </c>
       <c r="H113" s="26">
         <f>H111+Ausgaben!I179</f>
-        <v>3668.7</v>
+        <v>3553.7599999999998</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
@@ -7227,7 +7292,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>7064.7900000000263</v>
+        <v>6773.9300000000276</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -7963,127 +8028,127 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97">
-    <cfRule type="cellIs" dxfId="53" priority="68" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="68" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20:D22 D31 D41:D61">
-    <cfRule type="cellIs" dxfId="52" priority="6" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D89">
-    <cfRule type="cellIs" dxfId="51" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:F82">
-    <cfRule type="cellIs" dxfId="50" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:G81">
-    <cfRule type="cellIs" dxfId="49" priority="29" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101:G110">
-    <cfRule type="cellIs" dxfId="48" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="47" priority="88" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="88" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41:F42">
-    <cfRule type="cellIs" dxfId="46" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:G37 G38 E39:G40">
-    <cfRule type="cellIs" dxfId="45" priority="50" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="50" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:G49 G50:G51 E51:F51 F52:G52 G53:G58">
-    <cfRule type="cellIs" dxfId="44" priority="108" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="108" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E69:G71 G82:G83">
-    <cfRule type="cellIs" dxfId="43" priority="82" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="82" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E84:G89 D90:G98">
-    <cfRule type="cellIs" dxfId="42" priority="64" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:H3">
-    <cfRule type="cellIs" dxfId="41" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:H32">
-    <cfRule type="cellIs" dxfId="40" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:G25">
-    <cfRule type="cellIs" dxfId="39" priority="283" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="283" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:G60">
-    <cfRule type="cellIs" dxfId="38" priority="25" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72:G72">
-    <cfRule type="cellIs" dxfId="37" priority="80" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="80" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A93:C93">
-    <cfRule type="cellIs" dxfId="36" priority="196" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="196" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="cellIs" dxfId="35" priority="280" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="280" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
-    <cfRule type="cellIs" dxfId="34" priority="362" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="362" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H22">
-    <cfRule type="cellIs" dxfId="33" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:H31 G33:H33">
-    <cfRule type="cellIs" dxfId="32" priority="57" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="57" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10 B83">
-    <cfRule type="cellIs" dxfId="31" priority="210" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="210" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H27">
-    <cfRule type="cellIs" dxfId="30" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H40 C99:D100 H48:H110 G41:H47">
-    <cfRule type="cellIs" dxfId="29" priority="63" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="H34:H40 G41:H47 H48:H110 C99:D100">
+    <cfRule type="cellIs" dxfId="30" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8128,16 +8193,16 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="39"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
       <c r="J1" s="4"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3" t="s">
@@ -10226,14 +10291,22 @@
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="41"/>
-      <c r="B87" s="14"/>
+      <c r="B87" s="14">
+        <v>46204</v>
+      </c>
       <c r="C87" s="48">
         <v>82</v>
       </c>
-      <c r="D87" s="81"/>
-      <c r="E87" s="82"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="20"/>
+      <c r="D87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E87" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87" s="16"/>
+      <c r="G87" s="20">
+        <v>-12</v>
+      </c>
       <c r="H87" s="20"/>
       <c r="I87" s="20"/>
       <c r="J87" s="4"/>
@@ -10242,14 +10315,22 @@
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="41"/>
-      <c r="B88" s="14"/>
+      <c r="B88" s="14">
+        <v>46205</v>
+      </c>
       <c r="C88" s="48">
         <v>83</v>
       </c>
-      <c r="D88" s="81"/>
-      <c r="E88" s="82"/>
+      <c r="D88" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E88" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F88" s="19"/>
-      <c r="G88" s="20"/>
+      <c r="G88" s="20">
+        <v>-47</v>
+      </c>
       <c r="H88" s="20"/>
       <c r="I88" s="20"/>
       <c r="J88" s="4"/>
@@ -10258,14 +10339,22 @@
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="41"/>
-      <c r="B89" s="14"/>
+      <c r="B89" s="14">
+        <v>46205</v>
+      </c>
       <c r="C89" s="48">
         <v>84</v>
       </c>
-      <c r="D89" s="81"/>
-      <c r="E89" s="82"/>
+      <c r="D89" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E89" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F89" s="19"/>
-      <c r="G89" s="20"/>
+      <c r="G89" s="20">
+        <v>-89</v>
+      </c>
       <c r="H89" s="20"/>
       <c r="I89" s="20"/>
       <c r="J89" s="4"/>
@@ -10274,14 +10363,22 @@
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="41"/>
-      <c r="B90" s="14"/>
+      <c r="B90" s="14">
+        <v>46211</v>
+      </c>
       <c r="C90" s="48">
         <v>85</v>
       </c>
-      <c r="D90" s="3"/>
-      <c r="E90" s="82"/>
+      <c r="D90" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F90" s="19"/>
-      <c r="G90" s="20"/>
+      <c r="G90" s="20">
+        <v>-16.940000000000001</v>
+      </c>
       <c r="H90" s="20"/>
       <c r="I90" s="20"/>
       <c r="J90" s="4"/>
@@ -10290,46 +10387,70 @@
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="41"/>
-      <c r="B91" s="14"/>
+      <c r="B91" s="14">
+        <v>46214</v>
+      </c>
       <c r="C91" s="48">
         <v>86</v>
       </c>
-      <c r="D91" s="3"/>
-      <c r="E91" s="82"/>
+      <c r="D91" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F91" s="19"/>
       <c r="G91" s="20"/>
       <c r="H91" s="20"/>
-      <c r="I91" s="20"/>
+      <c r="I91" s="20">
+        <v>-190.09</v>
+      </c>
       <c r="J91" s="4"/>
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="41"/>
-      <c r="B92" s="14"/>
+      <c r="B92" s="14">
+        <v>46214</v>
+      </c>
       <c r="C92" s="48">
         <v>87</v>
       </c>
-      <c r="D92" s="3"/>
-      <c r="E92" s="82"/>
+      <c r="D92" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F92" s="19"/>
       <c r="G92" s="20"/>
       <c r="H92" s="20"/>
-      <c r="I92" s="20"/>
+      <c r="I92" s="20">
+        <v>-189.85</v>
+      </c>
       <c r="J92" s="4"/>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="41"/>
-      <c r="B93" s="14"/>
+      <c r="B93" s="14">
+        <v>46216</v>
+      </c>
       <c r="C93" s="48">
         <v>88</v>
       </c>
-      <c r="D93" s="3"/>
-      <c r="E93" s="82"/>
+      <c r="D93" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F93" s="19"/>
-      <c r="G93" s="20"/>
+      <c r="G93" s="20">
+        <v>-10.98</v>
+      </c>
       <c r="H93" s="20"/>
       <c r="I93" s="20"/>
       <c r="J93" s="4"/>
@@ -11710,7 +11831,7 @@
       </c>
       <c r="G179" s="32">
         <f>SUM(G3:G178)</f>
-        <v>-4574.9799999999968</v>
+        <v>-4750.899999999996</v>
       </c>
       <c r="H179" s="32">
         <f>SUM(H3:H178)</f>
@@ -11718,7 +11839,7 @@
       </c>
       <c r="I179" s="32">
         <f>SUM(I3:I178)</f>
-        <v>-3206.41</v>
+        <v>-3586.35</v>
       </c>
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
@@ -12632,152 +12753,157 @@
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A243 E33 E134:E145">
-    <cfRule type="cellIs" dxfId="28" priority="495" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="496" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130:B143">
-    <cfRule type="cellIs" dxfId="27" priority="478" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="479" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157:B245">
-    <cfRule type="cellIs" dxfId="26" priority="35" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="36" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C156 C158 C160 C162 C164 C166 C168 C174 C176">
-    <cfRule type="cellIs" dxfId="25" priority="36" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="37" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C178:C244 J180 I180:I245">
-    <cfRule type="cellIs" dxfId="24" priority="725" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="726" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D133">
-    <cfRule type="cellIs" dxfId="23" priority="493" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="494" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D150">
-    <cfRule type="cellIs" dxfId="22" priority="80" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="81" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D154:D155">
-    <cfRule type="cellIs" dxfId="21" priority="464" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="465" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D159:D164">
-    <cfRule type="cellIs" dxfId="20" priority="21" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="22" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D165:E166 D167:D168 C170:D170 D171:E171 C172:D172">
-    <cfRule type="cellIs" dxfId="19" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D178:E180">
-    <cfRule type="cellIs" dxfId="18" priority="30" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="31" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D180:H243">
-    <cfRule type="cellIs" dxfId="17" priority="677" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="678" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E126:E132 E147:E164">
-    <cfRule type="cellIs" dxfId="16" priority="16" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="14" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="14" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E58:E59">
     <cfRule type="cellIs" dxfId="13" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E59">
+  <conditionalFormatting sqref="E61">
     <cfRule type="cellIs" dxfId="12" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E61">
+  <conditionalFormatting sqref="E64">
     <cfRule type="cellIs" dxfId="11" priority="9" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E64">
+  <conditionalFormatting sqref="E66:E68">
     <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E66:E68">
+  <conditionalFormatting sqref="E72">
     <cfRule type="cellIs" dxfId="9" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72">
-    <cfRule type="cellIs" dxfId="8" priority="6" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E76:E81 E87:E89 E94:E124">
+    <cfRule type="cellIs" dxfId="8" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E81 E87:E124">
+  <conditionalFormatting sqref="E85">
     <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E167:E170">
-    <cfRule type="cellIs" dxfId="6" priority="18" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="19" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172:E177">
-    <cfRule type="cellIs" dxfId="5" priority="17" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="18" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="4" priority="15" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="16" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F77">
-    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99:F100">
-    <cfRule type="cellIs" dxfId="2" priority="138" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="139" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="cellIs" dxfId="1" priority="22" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="23" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E85">
+  <conditionalFormatting sqref="F87">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E147:E178 E126:E132 E134:E145 E58:E59 E72 E61 E64 E66:E68 E76:E81 E87:E124 E85" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E147:E178 E126:E132 E134:E145 E58:E59 E72 E61 E64 E66:E68 E76:E81 E85 E87:E89 E94:E124" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$L$1:$L$19</formula1>
     </dataValidation>
   </dataValidations>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55E1962-3B49-4FC7-88A8-E0A0856C2E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A133ED51-5374-4FD9-9F75-A6E914F6EE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Einnahmen" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="158">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -427,6 +427,87 @@
   </si>
   <si>
     <t>Shirts&amp;Sonnenschirm&amp;Sonstiges</t>
+  </si>
+  <si>
+    <t>Spende Musikergage</t>
+  </si>
+  <si>
+    <t>Sommerfest Selgros</t>
+  </si>
+  <si>
+    <t>Sommerfest</t>
+  </si>
+  <si>
+    <t>Escape Game Equipment</t>
+  </si>
+  <si>
+    <t>Sommerfest Fleisch</t>
+  </si>
+  <si>
+    <t>Sommerfest Käse</t>
+  </si>
+  <si>
+    <t>Sommerfest Ukr. Essen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einnahmen Escape Game </t>
+  </si>
+  <si>
+    <t>tzgl 7.7.</t>
+  </si>
+  <si>
+    <t>Sommerfest Einnahmen</t>
+  </si>
+  <si>
+    <t>Sommerfest Einnahmen SumUp Beleg fehlt noch</t>
+  </si>
+  <si>
+    <t>Sommerfest Brezeln</t>
+  </si>
+  <si>
+    <t>Sommerfest Drucke</t>
+  </si>
+  <si>
+    <t>Sommerfest Getränke</t>
+  </si>
+  <si>
+    <t>Miete WEG Versammlung Hochhaus</t>
+  </si>
+  <si>
+    <t>Sommerfest Gema</t>
+  </si>
+  <si>
+    <t>tzgl 21.7.</t>
+  </si>
+  <si>
+    <t>Konto gebühr</t>
+  </si>
+  <si>
+    <t>Sommerfest Raisch</t>
+  </si>
+  <si>
+    <t>tzgl 4.8.</t>
+  </si>
+  <si>
+    <t>Escape Game 9.8.</t>
+  </si>
+  <si>
+    <t>Getränke Heißwolf</t>
+  </si>
+  <si>
+    <t>tzgl 18.8.</t>
+  </si>
+  <si>
+    <t>tzgl 1.9.</t>
+  </si>
+  <si>
+    <t>Escape 6.9.</t>
+  </si>
+  <si>
+    <t>Gebühr EC Karte</t>
+  </si>
+  <si>
+    <t>Kinderschminken Sommerfest</t>
   </si>
 </sst>
 </file>
@@ -975,7 +1056,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1091,6 +1172,7 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1103,7 +1185,27 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="65">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -3949,17 +4051,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="57">
+    <format dxfId="61">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4063,17 +4165,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="60">
+    <format dxfId="64">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="58">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -5214,16 +5316,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3" t="s">
         <v>0</v>
@@ -6415,198 +6517,310 @@
       <c r="J53" s="2"/>
     </row>
     <row r="54" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="14"/>
+      <c r="A54" s="14">
+        <v>46216</v>
+      </c>
       <c r="B54" s="15">
         <v>50</v>
       </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="18"/>
+      <c r="C54" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E54" s="16"/>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
+      <c r="H54" s="17">
+        <v>75</v>
+      </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
     </row>
     <row r="55" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="14"/>
+      <c r="A55" s="14">
+        <v>46216</v>
+      </c>
       <c r="B55" s="15">
         <v>51</v>
       </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="18"/>
+      <c r="C55" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E55" s="16"/>
       <c r="F55" s="17"/>
       <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
+      <c r="H55" s="17">
+        <v>76</v>
+      </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
     </row>
     <row r="56" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14"/>
+      <c r="A56" s="14">
+        <v>46223</v>
+      </c>
       <c r="B56" s="15">
         <v>52</v>
       </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="18"/>
+      <c r="C56" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E56" s="16"/>
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
+      <c r="H56" s="17">
+        <v>1607.21</v>
+      </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
     </row>
     <row r="57" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="14"/>
+      <c r="A57" s="14">
+        <v>46223</v>
+      </c>
       <c r="B57" s="15">
         <v>53</v>
       </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="18"/>
+      <c r="C57" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E57" s="16"/>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
+      <c r="H57" s="17">
+        <v>38.950000000000003</v>
+      </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
     </row>
     <row r="58" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="14"/>
+      <c r="A58" s="14">
+        <v>46225</v>
+      </c>
       <c r="B58" s="15">
         <v>54</v>
       </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="18"/>
+      <c r="C58" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E58" s="16"/>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
+      <c r="H58" s="17">
+        <v>27.5</v>
+      </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
     </row>
     <row r="59" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="14"/>
+      <c r="A59" s="14">
+        <v>46226</v>
+      </c>
       <c r="B59" s="15">
         <v>55</v>
       </c>
-      <c r="C59" s="3"/>
-      <c r="D59" s="18"/>
+      <c r="C59" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E59" s="19"/>
       <c r="F59" s="17"/>
       <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
+      <c r="H59" s="17">
+        <v>12</v>
+      </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
     </row>
     <row r="60" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="14"/>
+      <c r="A60" s="14">
+        <v>46230</v>
+      </c>
       <c r="B60" s="15">
         <v>56</v>
       </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="18"/>
+      <c r="C60" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E60" s="19"/>
-      <c r="F60" s="17"/>
+      <c r="F60" s="17">
+        <v>1367.93</v>
+      </c>
       <c r="G60" s="17"/>
       <c r="H60" s="17"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
     </row>
     <row r="61" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="14"/>
+      <c r="A61" s="14">
+        <v>46232</v>
+      </c>
       <c r="B61" s="15">
         <v>57</v>
       </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="18"/>
+      <c r="C61" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E61" s="16"/>
       <c r="F61" s="17"/>
       <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
+      <c r="H61" s="17">
+        <v>105</v>
+      </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
     </row>
     <row r="62" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="14"/>
+      <c r="A62" s="14">
+        <v>46245</v>
+      </c>
       <c r="B62" s="48">
         <v>58</v>
       </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="18"/>
+      <c r="C62" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E62" s="16"/>
       <c r="F62" s="17"/>
       <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
+      <c r="H62" s="17">
+        <v>75</v>
+      </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
     </row>
     <row r="63" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="14"/>
+      <c r="A63" s="14">
+        <v>46246</v>
+      </c>
       <c r="B63" s="48">
         <v>59</v>
       </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="18"/>
+      <c r="C63" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E63" s="16"/>
       <c r="F63" s="17"/>
       <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
+      <c r="H63" s="17">
+        <v>17.5</v>
+      </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
     </row>
     <row r="64" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="14"/>
+      <c r="A64" s="14">
+        <v>46251</v>
+      </c>
       <c r="B64" s="48">
         <v>60</v>
       </c>
-      <c r="C64" s="37"/>
-      <c r="D64" s="18"/>
+      <c r="C64" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E64" s="16"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
+      <c r="H64" s="17">
+        <v>50</v>
+      </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
     </row>
     <row r="65" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="14"/>
+      <c r="A65" s="14">
+        <v>46258</v>
+      </c>
       <c r="B65" s="48">
         <v>61</v>
       </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="18"/>
+      <c r="C65" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E65" s="16"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
+      <c r="H65" s="17">
+        <v>94</v>
+      </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
     </row>
     <row r="66" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="14"/>
+      <c r="A66" s="14">
+        <v>46276</v>
+      </c>
       <c r="B66" s="48">
         <v>62</v>
       </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="18"/>
+      <c r="C66" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E66" s="16"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
+      <c r="H66" s="17">
+        <v>100</v>
+      </c>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
     </row>
     <row r="67" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="14"/>
+      <c r="A67" s="14">
+        <v>46279</v>
+      </c>
       <c r="B67" s="15">
         <v>63</v>
       </c>
-      <c r="C67" s="15"/>
-      <c r="D67" s="18"/>
+      <c r="C67" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E67" s="16"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
+      <c r="H67" s="17">
+        <v>15</v>
+      </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
     </row>
@@ -7221,7 +7435,7 @@
       </c>
       <c r="F111" s="26">
         <f>SUM(F3:F110)</f>
-        <v>5970.5700000000234</v>
+        <v>7338.5000000000236</v>
       </c>
       <c r="G111" s="26">
         <f>SUM(G3:G110)</f>
@@ -7229,7 +7443,7 @@
       </c>
       <c r="H111" s="26">
         <f>SUM(H3:H110)</f>
-        <v>7140.11</v>
+        <v>9433.27</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -7259,7 +7473,7 @@
       </c>
       <c r="F113" s="26">
         <f>F111+Ausgaben!G179</f>
-        <v>1219.6700000000274</v>
+        <v>2126.8600000000288</v>
       </c>
       <c r="G113" s="26">
         <f>G111+Ausgaben!H179</f>
@@ -7267,7 +7481,7 @@
       </c>
       <c r="H113" s="26">
         <f>H111+Ausgaben!I179</f>
-        <v>3553.7599999999998</v>
+        <v>4558.0600000000004</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
@@ -7292,7 +7506,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>6773.9300000000276</v>
+        <v>8685.4200000000292</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -8027,133 +8241,133 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97">
-    <cfRule type="cellIs" dxfId="54" priority="68" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D69:D77 E73:G77 A94:A97 D61:G68">
+    <cfRule type="cellIs" dxfId="58" priority="68" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D31 D41:D61">
-    <cfRule type="cellIs" dxfId="53" priority="6" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D20:D22 D31 D41:D59 D61:D67">
+    <cfRule type="cellIs" dxfId="57" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D89">
-    <cfRule type="cellIs" dxfId="52" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:F82">
-    <cfRule type="cellIs" dxfId="51" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:G81">
-    <cfRule type="cellIs" dxfId="50" priority="29" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101:G110">
-    <cfRule type="cellIs" dxfId="49" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="48" priority="88" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="88" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41:F42">
-    <cfRule type="cellIs" dxfId="47" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:G37 G38 E39:G40">
-    <cfRule type="cellIs" dxfId="46" priority="50" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="50" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:G49 G50:G51 E51:F51 F52:G52 G53:G58">
-    <cfRule type="cellIs" dxfId="45" priority="108" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="108" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E69:G71 G82:G83">
-    <cfRule type="cellIs" dxfId="44" priority="82" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="82" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E84:G89 D90:G98">
-    <cfRule type="cellIs" dxfId="43" priority="64" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:H3">
-    <cfRule type="cellIs" dxfId="42" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:H32">
-    <cfRule type="cellIs" dxfId="41" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:G25">
-    <cfRule type="cellIs" dxfId="40" priority="283" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="283" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:G60">
-    <cfRule type="cellIs" dxfId="39" priority="25" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72:G72">
-    <cfRule type="cellIs" dxfId="38" priority="80" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="80" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A93:C93">
-    <cfRule type="cellIs" dxfId="37" priority="196" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="196" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="cellIs" dxfId="36" priority="280" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="280" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
-    <cfRule type="cellIs" dxfId="35" priority="362" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="362" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H22">
-    <cfRule type="cellIs" dxfId="34" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:H31 G33:H33">
-    <cfRule type="cellIs" dxfId="33" priority="57" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="57" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10 B83">
-    <cfRule type="cellIs" dxfId="32" priority="210" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="210" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H27">
-    <cfRule type="cellIs" dxfId="31" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H40 G41:H47 H48:H110 C99:D100">
-    <cfRule type="cellIs" dxfId="30" priority="63" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D28 D31:D110" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D28 D31:D59 D61:D110" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$J$1:$J$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -8193,16 +8407,16 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="39"/>
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
       <c r="J1" s="4"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3" t="s">
@@ -10459,12 +10673,18 @@
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="41"/>
-      <c r="B94" s="14"/>
+      <c r="B94" s="14">
+        <v>46222</v>
+      </c>
       <c r="C94" s="48">
         <v>89</v>
       </c>
-      <c r="D94" s="3"/>
-      <c r="E94" s="82"/>
+      <c r="D94" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F94" s="19"/>
       <c r="G94" s="20"/>
       <c r="H94" s="20"/>
@@ -10475,12 +10695,18 @@
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="41"/>
-      <c r="B95" s="14"/>
+      <c r="B95" s="14">
+        <v>46222</v>
+      </c>
       <c r="C95" s="48">
         <v>90</v>
       </c>
-      <c r="D95" s="3"/>
-      <c r="E95" s="82"/>
+      <c r="D95" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F95" s="19"/>
       <c r="G95" s="20"/>
       <c r="H95" s="20"/>
@@ -10491,14 +10717,22 @@
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="41"/>
-      <c r="B96" s="14"/>
+      <c r="B96" s="14">
+        <v>46217</v>
+      </c>
       <c r="C96" s="48">
         <v>91</v>
       </c>
-      <c r="D96" s="81"/>
-      <c r="E96" s="82"/>
+      <c r="D96" s="81" t="s">
+        <v>132</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F96" s="19"/>
-      <c r="G96" s="20"/>
+      <c r="G96" s="20">
+        <v>-102.67</v>
+      </c>
       <c r="H96" s="20"/>
       <c r="I96" s="20"/>
       <c r="J96" s="4"/>
@@ -10507,112 +10741,167 @@
     </row>
     <row r="97" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="41"/>
-      <c r="B97" s="14"/>
+      <c r="B97" s="14">
+        <v>46218</v>
+      </c>
       <c r="C97" s="48">
         <v>92</v>
       </c>
-      <c r="D97" s="3"/>
-      <c r="E97" s="82"/>
+      <c r="D97" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="F97" s="19"/>
-      <c r="G97" s="20"/>
+      <c r="G97" s="20">
+        <v>-18.36</v>
+      </c>
       <c r="H97" s="20"/>
-      <c r="I97" s="20"/>
       <c r="J97" s="4"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
     <row r="98" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="41"/>
-      <c r="B98" s="14"/>
+      <c r="B98" s="14">
+        <v>46219</v>
+      </c>
       <c r="C98" s="48">
         <v>93</v>
       </c>
-      <c r="D98" s="3"/>
-      <c r="E98" s="82"/>
+      <c r="D98" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F98" s="19"/>
       <c r="G98" s="20"/>
       <c r="H98" s="20"/>
-      <c r="I98" s="20"/>
+      <c r="I98" s="20">
+        <v>-21.52</v>
+      </c>
       <c r="J98" s="4"/>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
     <row r="99" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="41"/>
-      <c r="B99" s="14"/>
+      <c r="B99" s="14">
+        <v>46219</v>
+      </c>
       <c r="C99" s="48">
         <v>94</v>
       </c>
-      <c r="D99" s="3"/>
-      <c r="E99" s="82"/>
+      <c r="D99" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F99" s="16"/>
       <c r="G99" s="20"/>
       <c r="H99" s="20"/>
-      <c r="I99" s="20"/>
+      <c r="I99" s="20">
+        <v>-30</v>
+      </c>
       <c r="J99" s="4"/>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
     <row r="100" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="41"/>
-      <c r="B100" s="14"/>
+      <c r="B100" s="14">
+        <v>46223</v>
+      </c>
       <c r="C100" s="48">
         <v>95</v>
       </c>
-      <c r="D100" s="3"/>
-      <c r="E100" s="82"/>
+      <c r="D100" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F100" s="16"/>
       <c r="G100" s="20"/>
       <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
+      <c r="I100" s="20">
+        <v>-219.7</v>
+      </c>
       <c r="J100" s="4"/>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
     </row>
     <row r="101" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="41"/>
-      <c r="B101" s="14"/>
+      <c r="B101" s="14">
+        <v>46223</v>
+      </c>
       <c r="C101" s="48">
         <v>96</v>
       </c>
-      <c r="D101" s="3"/>
-      <c r="E101" s="82"/>
+      <c r="D101" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F101" s="19"/>
       <c r="G101" s="20"/>
       <c r="H101" s="20"/>
-      <c r="I101" s="20"/>
+      <c r="I101" s="20">
+        <v>-55.35</v>
+      </c>
       <c r="J101" s="4"/>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
     </row>
     <row r="102" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="41"/>
-      <c r="B102" s="14"/>
+      <c r="B102" s="14">
+        <v>46223</v>
+      </c>
       <c r="C102" s="48">
         <v>97</v>
       </c>
-      <c r="D102" s="3"/>
-      <c r="E102" s="82"/>
+      <c r="D102" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F102" s="19"/>
       <c r="G102" s="20"/>
       <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
+      <c r="I102" s="20">
+        <v>-140.94</v>
+      </c>
       <c r="J102" s="4"/>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
     </row>
     <row r="103" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="41"/>
-      <c r="B103" s="14"/>
+      <c r="B103" s="14">
+        <v>46224</v>
+      </c>
       <c r="C103" s="48">
         <v>98</v>
       </c>
-      <c r="D103" s="3"/>
-      <c r="E103" s="82"/>
+      <c r="D103" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F103" s="19"/>
       <c r="G103" s="20"/>
       <c r="H103" s="20"/>
-      <c r="I103" s="20"/>
+      <c r="I103" s="20">
+        <v>-11</v>
+      </c>
       <c r="J103" s="4"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
@@ -10621,94 +10910,142 @@
     </row>
     <row r="104" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="41"/>
-      <c r="B104" s="14"/>
+      <c r="B104" s="14">
+        <v>46224</v>
+      </c>
       <c r="C104" s="48">
         <v>99</v>
       </c>
-      <c r="D104" s="81"/>
-      <c r="E104" s="82"/>
+      <c r="D104" s="81" t="s">
+        <v>143</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F104" s="19"/>
       <c r="G104" s="20"/>
       <c r="H104" s="20"/>
-      <c r="I104" s="20"/>
+      <c r="I104" s="20">
+        <v>-28.51</v>
+      </c>
       <c r="J104" s="4"/>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
     </row>
     <row r="105" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="41"/>
-      <c r="B105" s="14"/>
+      <c r="B105" s="14">
+        <v>46224</v>
+      </c>
       <c r="C105" s="48">
         <v>100</v>
       </c>
-      <c r="D105" s="3"/>
-      <c r="E105" s="82"/>
+      <c r="D105" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F105" s="19"/>
       <c r="G105" s="20"/>
       <c r="H105" s="20"/>
-      <c r="I105" s="20"/>
+      <c r="I105" s="20">
+        <v>-22.13</v>
+      </c>
       <c r="J105" s="4"/>
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
     </row>
     <row r="106" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="41"/>
-      <c r="B106" s="14"/>
+      <c r="B106" s="14">
+        <v>46224</v>
+      </c>
       <c r="C106" s="48">
         <v>101</v>
       </c>
-      <c r="D106" s="3"/>
-      <c r="E106" s="82"/>
+      <c r="D106" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F106" s="19"/>
       <c r="G106" s="20"/>
       <c r="H106" s="20"/>
-      <c r="I106" s="20"/>
+      <c r="I106" s="20">
+        <v>-411.28</v>
+      </c>
       <c r="J106" s="4"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
     <row r="107" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="41"/>
-      <c r="B107" s="14"/>
+      <c r="B107" s="14">
+        <v>46225</v>
+      </c>
       <c r="C107" s="48">
         <v>102</v>
       </c>
-      <c r="D107" s="81"/>
-      <c r="E107" s="82"/>
+      <c r="D107" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F107" s="19"/>
       <c r="G107" s="20"/>
       <c r="H107" s="20"/>
-      <c r="I107" s="20"/>
+      <c r="I107" s="20">
+        <v>-11.27</v>
+      </c>
       <c r="J107" s="4"/>
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
     </row>
     <row r="108" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="41"/>
-      <c r="B108" s="14"/>
+      <c r="B108" s="14">
+        <v>46227</v>
+      </c>
       <c r="C108" s="48">
         <v>103</v>
       </c>
-      <c r="D108" s="3"/>
-      <c r="E108" s="82"/>
+      <c r="D108" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F108" s="19"/>
       <c r="G108" s="20"/>
       <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
+      <c r="I108" s="20">
+        <v>-32.53</v>
+      </c>
       <c r="J108" s="4"/>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
     </row>
     <row r="109" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="41"/>
-      <c r="B109" s="14"/>
+      <c r="B109" s="14">
+        <v>46230</v>
+      </c>
       <c r="C109" s="48">
         <v>104</v>
       </c>
-      <c r="D109" s="3"/>
-      <c r="E109" s="82"/>
+      <c r="D109" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E109" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F109" s="19"/>
-      <c r="G109" s="20"/>
+      <c r="G109" s="20">
+        <v>-4.99</v>
+      </c>
       <c r="H109" s="20"/>
       <c r="I109" s="20"/>
       <c r="J109" s="4"/>
@@ -10717,46 +11054,70 @@
     </row>
     <row r="110" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="41"/>
-      <c r="B110" s="14"/>
+      <c r="B110" s="14">
+        <v>46234</v>
+      </c>
       <c r="C110" s="48">
         <v>105</v>
       </c>
-      <c r="D110" s="3"/>
-      <c r="E110" s="82"/>
+      <c r="D110" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E110" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F110" s="19"/>
       <c r="G110" s="20"/>
       <c r="H110" s="20"/>
-      <c r="I110" s="20"/>
+      <c r="I110" s="20">
+        <v>-2.5</v>
+      </c>
       <c r="J110" s="4"/>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
     </row>
     <row r="111" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="41"/>
-      <c r="B111" s="14"/>
+      <c r="B111" s="14">
+        <v>46237</v>
+      </c>
       <c r="C111" s="48">
         <v>106</v>
       </c>
-      <c r="D111" s="3"/>
-      <c r="E111" s="82"/>
+      <c r="D111" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F111" s="19"/>
       <c r="G111" s="20"/>
       <c r="H111" s="20"/>
-      <c r="I111" s="20"/>
+      <c r="I111" s="20">
+        <v>-96.63</v>
+      </c>
       <c r="J111" s="4"/>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
     </row>
     <row r="112" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="41"/>
-      <c r="B112" s="14"/>
+      <c r="B112" s="14">
+        <v>46237</v>
+      </c>
       <c r="C112" s="48">
         <v>107</v>
       </c>
-      <c r="D112" s="3"/>
-      <c r="E112" s="82"/>
-      <c r="F112" s="19"/>
-      <c r="G112" s="20"/>
+      <c r="D112" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E112" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F112" s="16"/>
+      <c r="G112" s="20">
+        <v>-12</v>
+      </c>
       <c r="H112" s="20"/>
       <c r="I112" s="20"/>
       <c r="J112" s="4"/>
@@ -10765,14 +11126,22 @@
     </row>
     <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="41"/>
-      <c r="B113" s="14"/>
+      <c r="B113" s="14">
+        <v>46238</v>
+      </c>
       <c r="C113" s="48">
         <v>108</v>
       </c>
-      <c r="D113" s="81"/>
-      <c r="E113" s="82"/>
+      <c r="D113" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E113" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F113" s="19"/>
-      <c r="G113" s="20"/>
+      <c r="G113" s="20">
+        <v>-47</v>
+      </c>
       <c r="H113" s="20"/>
       <c r="I113" s="20"/>
       <c r="J113" s="4"/>
@@ -10781,14 +11150,22 @@
     </row>
     <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="41"/>
-      <c r="B114" s="14"/>
+      <c r="B114" s="14">
+        <v>46238</v>
+      </c>
       <c r="C114" s="48">
         <v>109</v>
       </c>
-      <c r="D114" s="3"/>
-      <c r="E114" s="82"/>
+      <c r="D114" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E114" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F114" s="19"/>
-      <c r="G114" s="20"/>
+      <c r="G114" s="20">
+        <v>-89</v>
+      </c>
       <c r="H114" s="20"/>
       <c r="I114" s="20"/>
       <c r="J114" s="4"/>
@@ -10797,14 +11174,22 @@
     </row>
     <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="41"/>
-      <c r="B115" s="14"/>
+      <c r="B115" s="14">
+        <v>46238</v>
+      </c>
       <c r="C115" s="48">
         <v>110</v>
       </c>
-      <c r="D115" s="3"/>
-      <c r="E115" s="82"/>
+      <c r="D115" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F115" s="19"/>
-      <c r="G115" s="20"/>
+      <c r="G115" s="20">
+        <v>-4.67</v>
+      </c>
       <c r="H115" s="20"/>
       <c r="I115" s="20"/>
       <c r="J115" s="4"/>
@@ -10813,62 +11198,94 @@
     </row>
     <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="41"/>
-      <c r="B116" s="14"/>
+      <c r="B116" s="14">
+        <v>46246</v>
+      </c>
       <c r="C116" s="48">
         <v>111</v>
       </c>
-      <c r="D116" s="3"/>
-      <c r="E116" s="82"/>
+      <c r="D116" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E116" s="82" t="s">
+        <v>13</v>
+      </c>
       <c r="F116" s="19"/>
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
-      <c r="I116" s="20"/>
+      <c r="I116" s="20">
+        <v>-15</v>
+      </c>
       <c r="J116" s="4"/>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
     </row>
     <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="41"/>
-      <c r="B117" s="14"/>
+      <c r="B117" s="14">
+        <v>46251</v>
+      </c>
       <c r="C117" s="48">
         <v>112</v>
       </c>
-      <c r="D117" s="3"/>
-      <c r="E117" s="82"/>
+      <c r="D117" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F117" s="16"/>
       <c r="G117" s="20"/>
       <c r="H117" s="20"/>
-      <c r="I117" s="20"/>
+      <c r="I117" s="20">
+        <v>-180</v>
+      </c>
       <c r="J117" s="4"/>
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
     </row>
     <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="41"/>
-      <c r="B118" s="14"/>
+      <c r="B118" s="14">
+        <v>46252</v>
+      </c>
       <c r="C118" s="48">
         <v>113</v>
       </c>
-      <c r="D118" s="3"/>
-      <c r="E118" s="21"/>
+      <c r="D118" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F118" s="19"/>
       <c r="G118" s="20"/>
       <c r="H118" s="20"/>
-      <c r="I118" s="20"/>
+      <c r="I118" s="20">
+        <v>-10.5</v>
+      </c>
       <c r="J118" s="4"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
     </row>
     <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="41"/>
-      <c r="B119" s="14"/>
+      <c r="B119" s="14">
+        <v>46252</v>
+      </c>
       <c r="C119" s="48">
         <v>114</v>
       </c>
-      <c r="D119" s="3"/>
-      <c r="E119" s="82"/>
+      <c r="D119" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F119" s="19"/>
-      <c r="G119" s="20"/>
+      <c r="G119" s="20">
+        <v>-4.95</v>
+      </c>
       <c r="H119" s="20"/>
       <c r="I119" s="20"/>
       <c r="J119" s="4"/>
@@ -10877,14 +11294,22 @@
     </row>
     <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="41"/>
-      <c r="B120" s="14"/>
+      <c r="B120" s="14">
+        <v>46253</v>
+      </c>
       <c r="C120" s="48">
         <v>115</v>
       </c>
-      <c r="D120" s="3"/>
-      <c r="E120" s="82"/>
+      <c r="D120" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F120" s="19"/>
-      <c r="G120" s="20"/>
+      <c r="G120" s="20">
+        <v>-5.49</v>
+      </c>
       <c r="H120" s="20"/>
       <c r="I120" s="20"/>
       <c r="J120" s="4"/>
@@ -10893,14 +11318,22 @@
     </row>
     <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="41"/>
-      <c r="B121" s="14"/>
+      <c r="B121" s="14">
+        <v>46258</v>
+      </c>
       <c r="C121" s="48">
         <v>116</v>
       </c>
-      <c r="D121" s="3"/>
-      <c r="E121" s="82"/>
+      <c r="D121" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F121" s="19"/>
-      <c r="G121" s="20"/>
+      <c r="G121" s="20">
+        <v>-18.62</v>
+      </c>
       <c r="H121" s="20"/>
       <c r="I121" s="20"/>
       <c r="J121" s="4"/>
@@ -10909,14 +11342,22 @@
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="41"/>
-      <c r="B122" s="14"/>
+      <c r="B122" s="14">
+        <v>46261</v>
+      </c>
       <c r="C122" s="48">
         <v>117</v>
       </c>
-      <c r="D122" s="3"/>
-      <c r="E122" s="82"/>
+      <c r="D122" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E122" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F122" s="19"/>
-      <c r="G122" s="20"/>
+      <c r="G122" s="20">
+        <v>-4.99</v>
+      </c>
       <c r="H122" s="20"/>
       <c r="I122" s="20"/>
       <c r="J122" s="4"/>
@@ -10925,14 +11366,22 @@
     </row>
     <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="41"/>
-      <c r="B123" s="14"/>
+      <c r="B123" s="14">
+        <v>46267</v>
+      </c>
       <c r="C123" s="48">
         <v>118</v>
       </c>
-      <c r="D123" s="3"/>
-      <c r="E123" s="82"/>
+      <c r="D123" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E123" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F123" s="19"/>
-      <c r="G123" s="20"/>
+      <c r="G123" s="20">
+        <v>-47</v>
+      </c>
       <c r="H123" s="20"/>
       <c r="I123" s="20"/>
       <c r="J123" s="4"/>
@@ -10941,14 +11390,22 @@
     </row>
     <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="41"/>
-      <c r="B124" s="14"/>
+      <c r="B124" s="14">
+        <v>46267</v>
+      </c>
       <c r="C124" s="48">
         <v>119</v>
       </c>
-      <c r="D124" s="3"/>
-      <c r="E124" s="82"/>
+      <c r="D124" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E124" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F124" s="19"/>
-      <c r="G124" s="20"/>
+      <c r="G124" s="20">
+        <v>-89</v>
+      </c>
       <c r="H124" s="20"/>
       <c r="I124" s="20"/>
       <c r="J124" s="4"/>
@@ -10957,14 +11414,22 @@
     </row>
     <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="41"/>
-      <c r="B125" s="14"/>
+      <c r="B125" s="14">
+        <v>46268</v>
+      </c>
       <c r="C125" s="48">
         <v>120</v>
       </c>
-      <c r="D125" s="3"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="19"/>
-      <c r="G125" s="20"/>
+      <c r="D125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E125" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F125" s="16"/>
+      <c r="G125" s="20">
+        <v>-12</v>
+      </c>
       <c r="H125" s="20"/>
       <c r="I125" s="20"/>
       <c r="J125" s="4"/>
@@ -11831,7 +12296,7 @@
       </c>
       <c r="G179" s="32">
         <f>SUM(G3:G178)</f>
-        <v>-4750.899999999996</v>
+        <v>-5211.6399999999949</v>
       </c>
       <c r="H179" s="32">
         <f>SUM(H3:H178)</f>
@@ -11839,7 +12304,7 @@
       </c>
       <c r="I179" s="32">
         <f>SUM(I3:I178)</f>
-        <v>-3586.35</v>
+        <v>-4875.21</v>
       </c>
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
@@ -12753,157 +13218,177 @@
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A243 E33 E134:E145">
-    <cfRule type="cellIs" dxfId="29" priority="496" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="500" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130:B143">
-    <cfRule type="cellIs" dxfId="28" priority="479" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="483" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157:B245">
-    <cfRule type="cellIs" dxfId="27" priority="36" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="40" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C156 C158 C160 C162 C164 C166 C168 C174 C176">
-    <cfRule type="cellIs" dxfId="26" priority="37" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="41" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C178:C244 J180 I180:I245">
-    <cfRule type="cellIs" dxfId="25" priority="726" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="730" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D133">
-    <cfRule type="cellIs" dxfId="24" priority="494" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="498" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D150">
-    <cfRule type="cellIs" dxfId="23" priority="81" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="85" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D154:D155">
-    <cfRule type="cellIs" dxfId="22" priority="465" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="469" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D159:D164">
-    <cfRule type="cellIs" dxfId="21" priority="22" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="26" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D165:E166 D167:D168 C170:D170 D171:E171 C172:D172">
-    <cfRule type="cellIs" dxfId="20" priority="29" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="33" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D178:E180">
-    <cfRule type="cellIs" dxfId="19" priority="31" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="35" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D180:H243">
-    <cfRule type="cellIs" dxfId="18" priority="678" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="682" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E126:E132 E147:E164">
-    <cfRule type="cellIs" dxfId="17" priority="17" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="21" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="16" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="15" priority="14" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="18" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
+    <cfRule type="cellIs" dxfId="18" priority="16" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E58:E59">
+    <cfRule type="cellIs" dxfId="17" priority="15" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61">
+    <cfRule type="cellIs" dxfId="16" priority="14" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E64">
+    <cfRule type="cellIs" dxfId="15" priority="13" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E66:E68">
     <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E59">
+  <conditionalFormatting sqref="E72">
     <cfRule type="cellIs" dxfId="13" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E61">
-    <cfRule type="cellIs" dxfId="12" priority="10" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E64">
-    <cfRule type="cellIs" dxfId="11" priority="9" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E66:E68">
-    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E72">
-    <cfRule type="cellIs" dxfId="9" priority="7" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E81 E87:E89 E94:E124">
-    <cfRule type="cellIs" dxfId="8" priority="3" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E76:E81 E87:E89 E112:E114 E116 E123:E125">
+    <cfRule type="cellIs" dxfId="12" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E85">
-    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E109:E110">
+    <cfRule type="cellIs" dxfId="10" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E167:E170">
-    <cfRule type="cellIs" dxfId="6" priority="19" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="23" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172:E177">
-    <cfRule type="cellIs" dxfId="5" priority="18" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="22" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="4" priority="16" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="20" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F77">
-    <cfRule type="cellIs" dxfId="3" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F87">
+    <cfRule type="cellIs" dxfId="5" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99:F100">
-    <cfRule type="cellIs" dxfId="2" priority="139" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="143" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F112">
+    <cfRule type="cellIs" dxfId="3" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="cellIs" dxfId="1" priority="23" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F87">
+  <conditionalFormatting sqref="E122">
+    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F125">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E147:E178 E126:E132 E134:E145 E58:E59 E72 E61 E64 E66:E68 E76:E81 E85 E87:E89 E94:E124" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E147:E178 E134:E145 E58:E59 E72 E61 E64 E66:E68 E76:E81 E85 E87:E89 E109:E110 E112:E114 E116 E122:E132" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$L$1:$L$19</formula1>
     </dataValidation>
   </dataValidations>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A133ED51-5374-4FD9-9F75-A6E914F6EE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADF70E1-883A-47F3-BD98-905CED542C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="159">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -508,6 +508,9 @@
   </si>
   <si>
     <t>Kinderschminken Sommerfest</t>
+  </si>
+  <si>
+    <t>tzgl 15.9.</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1188,12 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="66">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -4051,17 +4059,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="61">
+    <format dxfId="62">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="61">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4165,17 +4173,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="64">
+    <format dxfId="65">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="63">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6825,16 +6833,24 @@
       <c r="J67" s="2"/>
     </row>
     <row r="68" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
+      <c r="A68" s="14">
+        <v>46281</v>
+      </c>
       <c r="B68" s="48">
         <v>64</v>
       </c>
-      <c r="C68" s="37"/>
-      <c r="D68" s="18"/>
+      <c r="C68" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E68" s="16"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
+      <c r="H68" s="17">
+        <v>93</v>
+      </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
     </row>
@@ -7443,7 +7459,7 @@
       </c>
       <c r="H111" s="26">
         <f>SUM(H3:H110)</f>
-        <v>9433.27</v>
+        <v>9526.27</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -7473,7 +7489,7 @@
       </c>
       <c r="F113" s="26">
         <f>F111+Ausgaben!G179</f>
-        <v>2126.8600000000288</v>
+        <v>2121.870000000029</v>
       </c>
       <c r="G113" s="26">
         <f>G111+Ausgaben!H179</f>
@@ -7481,7 +7497,7 @@
       </c>
       <c r="H113" s="26">
         <f>H111+Ausgaben!I179</f>
-        <v>4558.0600000000004</v>
+        <v>4651.0600000000004</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
@@ -7506,7 +7522,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>8685.4200000000292</v>
+        <v>8773.4300000000294</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -8241,128 +8257,128 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D69:D77 E73:G77 A94:A97 D61:G68">
-    <cfRule type="cellIs" dxfId="58" priority="68" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 E73:G77 A94:A97 D68:D77">
+    <cfRule type="cellIs" dxfId="59" priority="68" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D31 D41:D59 D61:D67">
-    <cfRule type="cellIs" dxfId="57" priority="6" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D20:D22 D31 D41:D59 D61:D68">
+    <cfRule type="cellIs" dxfId="58" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D89">
-    <cfRule type="cellIs" dxfId="56" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="57" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:F82">
-    <cfRule type="cellIs" dxfId="55" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:G81">
-    <cfRule type="cellIs" dxfId="54" priority="29" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101:G110">
-    <cfRule type="cellIs" dxfId="53" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="52" priority="88" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="88" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41:F42">
-    <cfRule type="cellIs" dxfId="51" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:G37 G38 E39:G40">
-    <cfRule type="cellIs" dxfId="50" priority="50" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="50" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:G49 G50:G51 E51:F51 F52:G52 G53:G58">
-    <cfRule type="cellIs" dxfId="49" priority="108" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="108" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E69:G71 G82:G83">
-    <cfRule type="cellIs" dxfId="48" priority="82" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="82" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E84:G89 D90:G98">
-    <cfRule type="cellIs" dxfId="47" priority="64" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="64" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:H3">
-    <cfRule type="cellIs" dxfId="46" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:H32">
-    <cfRule type="cellIs" dxfId="45" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:G25">
-    <cfRule type="cellIs" dxfId="44" priority="283" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="283" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:G60">
-    <cfRule type="cellIs" dxfId="43" priority="25" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72:G72">
-    <cfRule type="cellIs" dxfId="42" priority="80" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="80" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A93:C93">
-    <cfRule type="cellIs" dxfId="41" priority="196" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="196" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="cellIs" dxfId="40" priority="280" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="280" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
-    <cfRule type="cellIs" dxfId="39" priority="362" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="362" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H22">
-    <cfRule type="cellIs" dxfId="38" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:H31 G33:H33">
-    <cfRule type="cellIs" dxfId="37" priority="57" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="57" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10 B83">
-    <cfRule type="cellIs" dxfId="36" priority="210" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="210" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H27">
-    <cfRule type="cellIs" dxfId="35" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:H40 G41:H47 H48:H110 C99:D100">
-    <cfRule type="cellIs" dxfId="34" priority="63" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11438,14 +11454,22 @@
     </row>
     <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="41"/>
-      <c r="B126" s="14"/>
+      <c r="B126" s="14">
+        <v>46268</v>
+      </c>
       <c r="C126" s="48">
         <v>121</v>
       </c>
-      <c r="D126" s="3"/>
-      <c r="E126" s="82"/>
+      <c r="D126" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E126" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F126" s="19"/>
-      <c r="G126" s="20"/>
+      <c r="G126" s="20">
+        <v>-4.99</v>
+      </c>
       <c r="H126" s="20"/>
       <c r="I126" s="20"/>
       <c r="J126" s="4"/>
@@ -12296,7 +12320,7 @@
       </c>
       <c r="G179" s="32">
         <f>SUM(G3:G178)</f>
-        <v>-5211.6399999999949</v>
+        <v>-5216.6299999999947</v>
       </c>
       <c r="H179" s="32">
         <f>SUM(H3:H178)</f>
@@ -13218,171 +13242,176 @@
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A243 E33 E134:E145">
-    <cfRule type="cellIs" dxfId="33" priority="500" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="501" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130:B143">
-    <cfRule type="cellIs" dxfId="32" priority="483" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="484" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157:B245">
-    <cfRule type="cellIs" dxfId="31" priority="40" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="41" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C156 C158 C160 C162 C164 C166 C168 C174 C176">
-    <cfRule type="cellIs" dxfId="30" priority="41" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="42" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C178:C244 J180 I180:I245">
-    <cfRule type="cellIs" dxfId="29" priority="730" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="731" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D133">
-    <cfRule type="cellIs" dxfId="28" priority="498" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="499" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D150">
-    <cfRule type="cellIs" dxfId="27" priority="85" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="86" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D154:D155">
-    <cfRule type="cellIs" dxfId="26" priority="469" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="470" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D159:D164">
-    <cfRule type="cellIs" dxfId="25" priority="26" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D165:E166 D167:D168 C170:D170 D171:E171 C172:D172">
-    <cfRule type="cellIs" dxfId="24" priority="33" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="34" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D178:E180">
-    <cfRule type="cellIs" dxfId="23" priority="35" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="36" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D180:H243">
-    <cfRule type="cellIs" dxfId="22" priority="682" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="683" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E126:E132 E147:E164">
-    <cfRule type="cellIs" dxfId="21" priority="21" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E147:E164">
+    <cfRule type="cellIs" dxfId="22" priority="22" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="20" priority="17" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="18" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="19" priority="18" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="19" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
+    <cfRule type="cellIs" dxfId="19" priority="17" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E58:E59">
     <cfRule type="cellIs" dxfId="18" priority="16" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E59">
+  <conditionalFormatting sqref="E61">
     <cfRule type="cellIs" dxfId="17" priority="15" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E61">
+  <conditionalFormatting sqref="E64">
     <cfRule type="cellIs" dxfId="16" priority="14" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E64">
+  <conditionalFormatting sqref="E66:E68">
     <cfRule type="cellIs" dxfId="15" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E66:E68">
+  <conditionalFormatting sqref="E72">
     <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E72">
-    <cfRule type="cellIs" dxfId="13" priority="11" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E76:E81 E87:E89 E112:E114 E116">
+    <cfRule type="cellIs" dxfId="13" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76:E81 E87:E89 E112:E114 E116 E123:E125">
+  <conditionalFormatting sqref="E85">
     <cfRule type="cellIs" dxfId="12" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E85">
-    <cfRule type="cellIs" dxfId="11" priority="6" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E109:E110">
+    <cfRule type="cellIs" dxfId="11" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E109:E110">
-    <cfRule type="cellIs" dxfId="10" priority="4" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E122:E125 E127:E132">
+    <cfRule type="cellIs" dxfId="10" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E167:E170">
-    <cfRule type="cellIs" dxfId="9" priority="23" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="24" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172:E177">
-    <cfRule type="cellIs" dxfId="8" priority="22" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="23" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="7" priority="20" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="21" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F77">
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87">
-    <cfRule type="cellIs" dxfId="5" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99:F100">
-    <cfRule type="cellIs" dxfId="4" priority="143" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="144" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="cellIs" dxfId="3" priority="3" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="cellIs" dxfId="2" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E122">
+  <conditionalFormatting sqref="F125">
     <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F125">
+  <conditionalFormatting sqref="E126">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADF70E1-883A-47F3-BD98-905CED542C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DD4820-5413-4FD0-B5C0-5F52EE6D9406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,9 +18,9 @@
     <sheet name="Gesamt" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Ausgaben!$B$2:$J$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Ausgaben!$B$2:$J$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Einnahmen!$A$2:$H$107</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Ausgaben!$A$1:$I$178</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Ausgaben!$A$1:$I$179</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Einnahmen!$A$1:$H$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="165">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -511,6 +511,24 @@
   </si>
   <si>
     <t>tzgl 15.9.</t>
+  </si>
+  <si>
+    <t>tzgl 29.9.</t>
+  </si>
+  <si>
+    <t>Escape Room Volleyball</t>
+  </si>
+  <si>
+    <t>122a</t>
+  </si>
+  <si>
+    <t>Bankgebuehr KSK</t>
+  </si>
+  <si>
+    <t>Trauerkarte Natly</t>
+  </si>
+  <si>
+    <t>Weihnachtsfeier Taschen</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1206,17 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="68">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1669,7 +1697,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bernd Wild" refreshedDate="45318.474550578707" createdVersion="4" refreshedVersion="8" minRefreshableVersion="3" recordCount="168" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="E2:I174" sheet="Ausgaben"/>
+    <worksheetSource ref="E2:I175" sheet="Ausgaben"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="Zweck II" numFmtId="0">
@@ -4059,17 +4087,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="62">
+    <format dxfId="64">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="61">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4173,17 +4201,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="65">
+    <format dxfId="67">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="64">
+    <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6855,30 +6883,45 @@
       <c r="J68" s="2"/>
     </row>
     <row r="69" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="14"/>
+      <c r="A69" s="14">
+        <v>46295</v>
+      </c>
       <c r="B69" s="15">
         <v>65</v>
       </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="18"/>
+      <c r="C69" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E69" s="16"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17"/>
-      <c r="H69" s="17"/>
+      <c r="H69" s="17">
+        <v>118</v>
+      </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
     </row>
     <row r="70" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="14"/>
+      <c r="A70" s="14">
+        <v>46300</v>
+      </c>
       <c r="B70" s="15">
         <v>66</v>
       </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="17"/>
+      <c r="C70" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="19"/>
+      <c r="F70" s="17">
+        <v>30</v>
+      </c>
       <c r="G70" s="17"/>
-      <c r="H70" s="17"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
     </row>
@@ -7451,7 +7494,7 @@
       </c>
       <c r="F111" s="26">
         <f>SUM(F3:F110)</f>
-        <v>7338.5000000000236</v>
+        <v>7368.5000000000236</v>
       </c>
       <c r="G111" s="26">
         <f>SUM(G3:G110)</f>
@@ -7459,7 +7502,7 @@
       </c>
       <c r="H111" s="26">
         <f>SUM(H3:H110)</f>
-        <v>9526.27</v>
+        <v>9644.27</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -7484,20 +7527,20 @@
       <c r="C113" s="23"/>
       <c r="D113" s="45"/>
       <c r="E113" s="26">
-        <f>E111+Ausgaben!F179</f>
+        <f>E111+Ausgaben!F180</f>
         <v>0</v>
       </c>
       <c r="F113" s="26">
-        <f>F111+Ausgaben!G179</f>
-        <v>2121.870000000029</v>
+        <f>F111+Ausgaben!G180</f>
+        <v>1863.5200000000286</v>
       </c>
       <c r="G113" s="26">
-        <f>G111+Ausgaben!H179</f>
+        <f>G111+Ausgaben!H180</f>
         <v>2000.5</v>
       </c>
       <c r="H113" s="26">
-        <f>H111+Ausgaben!I179</f>
-        <v>4651.0600000000004</v>
+        <f>H111+Ausgaben!I180</f>
+        <v>4761.5600000000004</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
@@ -7522,7 +7565,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>8773.4300000000294</v>
+        <v>8625.580000000029</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -8257,128 +8300,138 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 E73:G77 A94:A97 D68:D77">
-    <cfRule type="cellIs" dxfId="59" priority="68" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 E73:G77 A94:A97 H48:H69 H71:H110 F70">
+    <cfRule type="cellIs" dxfId="61" priority="70" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D31 D41:D59 D61:D68">
-    <cfRule type="cellIs" dxfId="58" priority="6" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D20:D22 D31 D41:D59 D61:D77">
+    <cfRule type="cellIs" dxfId="60" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D89">
-    <cfRule type="cellIs" dxfId="57" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:F82">
-    <cfRule type="cellIs" dxfId="56" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="58" priority="30" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:G81">
-    <cfRule type="cellIs" dxfId="55" priority="29" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="57" priority="31" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101:G110">
-    <cfRule type="cellIs" dxfId="54" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="53" priority="88" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="55" priority="90" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41:F42">
-    <cfRule type="cellIs" dxfId="52" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:G37 G38 E39:G40">
-    <cfRule type="cellIs" dxfId="51" priority="50" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="52" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:G49 G50:G51 E51:F51 F52:G52 G53:G58">
-    <cfRule type="cellIs" dxfId="50" priority="108" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="110" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E69:G71 G82:G83">
-    <cfRule type="cellIs" dxfId="49" priority="82" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E71:G71 G82:G83">
+    <cfRule type="cellIs" dxfId="51" priority="84" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E84:G89 D90:G98">
-    <cfRule type="cellIs" dxfId="48" priority="64" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="66" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:H3">
-    <cfRule type="cellIs" dxfId="47" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="15" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:H32">
-    <cfRule type="cellIs" dxfId="46" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:G25">
-    <cfRule type="cellIs" dxfId="45" priority="283" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="285" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:G60">
-    <cfRule type="cellIs" dxfId="44" priority="25" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72:G72">
-    <cfRule type="cellIs" dxfId="43" priority="80" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="82" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A93:C93">
-    <cfRule type="cellIs" dxfId="42" priority="196" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="198" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="cellIs" dxfId="41" priority="280" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="282" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
-    <cfRule type="cellIs" dxfId="40" priority="362" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="364" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H22">
-    <cfRule type="cellIs" dxfId="39" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:H31 G33:H33">
-    <cfRule type="cellIs" dxfId="38" priority="57" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="59" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10 B83">
-    <cfRule type="cellIs" dxfId="37" priority="210" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="212" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H27">
-    <cfRule type="cellIs" dxfId="36" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H40 G41:H47 H48:H110 C99:D100">
-    <cfRule type="cellIs" dxfId="35" priority="63" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="H34:H40 G41:H47 C99:D100">
+    <cfRule type="cellIs" dxfId="37" priority="65" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D69:G69">
+    <cfRule type="cellIs" dxfId="36" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G70">
+    <cfRule type="cellIs" dxfId="35" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8404,7 +8457,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:IL245"/>
+  <dimension ref="A1:IL246"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="43" customWidth="1"/>
@@ -11478,14 +11531,22 @@
     </row>
     <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="41"/>
-      <c r="B127" s="14"/>
+      <c r="B127" s="14">
+        <v>46293</v>
+      </c>
       <c r="C127" s="48">
         <v>122</v>
       </c>
-      <c r="D127" s="81"/>
-      <c r="E127" s="82"/>
+      <c r="D127" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E127" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F127" s="19"/>
-      <c r="G127" s="20"/>
+      <c r="G127" s="20">
+        <v>-8.9700000000000006</v>
+      </c>
       <c r="H127" s="20"/>
       <c r="I127" s="20"/>
       <c r="J127" s="4"/>
@@ -11494,30 +11555,46 @@
     </row>
     <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="41"/>
-      <c r="B128" s="14"/>
-      <c r="C128" s="48">
-        <v>123</v>
-      </c>
-      <c r="D128" s="3"/>
-      <c r="E128" s="82"/>
+      <c r="B128" s="14">
+        <v>46295</v>
+      </c>
+      <c r="C128" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="D128" s="81" t="s">
+        <v>162</v>
+      </c>
+      <c r="E128" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F128" s="19"/>
       <c r="G128" s="20"/>
       <c r="H128" s="20"/>
-      <c r="I128" s="20"/>
+      <c r="I128" s="20">
+        <v>-7.5</v>
+      </c>
       <c r="J128" s="4"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
     </row>
     <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="41"/>
-      <c r="B129" s="14"/>
+      <c r="B129" s="14">
+        <v>46297</v>
+      </c>
       <c r="C129" s="48">
-        <v>124</v>
-      </c>
-      <c r="D129" s="3"/>
-      <c r="E129" s="82"/>
+        <v>123</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E129" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F129" s="19"/>
-      <c r="G129" s="20"/>
+      <c r="G129" s="20">
+        <v>-47</v>
+      </c>
       <c r="H129" s="20"/>
       <c r="I129" s="20"/>
       <c r="J129" s="4"/>
@@ -11526,14 +11603,22 @@
     </row>
     <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="41"/>
-      <c r="B130" s="14"/>
+      <c r="B130" s="14">
+        <v>46297</v>
+      </c>
       <c r="C130" s="48">
-        <v>125</v>
-      </c>
-      <c r="D130" s="3"/>
-      <c r="E130" s="82"/>
+        <v>124</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E130" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F130" s="19"/>
-      <c r="G130" s="20"/>
+      <c r="G130" s="20">
+        <v>-89</v>
+      </c>
       <c r="H130" s="20"/>
       <c r="I130" s="20"/>
       <c r="J130" s="4"/>
@@ -11542,14 +11627,22 @@
     </row>
     <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="41"/>
-      <c r="B131" s="14"/>
+      <c r="B131" s="14">
+        <v>46297</v>
+      </c>
       <c r="C131" s="48">
-        <v>126</v>
-      </c>
-      <c r="D131" s="3"/>
-      <c r="E131" s="82"/>
-      <c r="F131" s="19"/>
-      <c r="G131" s="20"/>
+        <v>125</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E131" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F131" s="16"/>
+      <c r="G131" s="20">
+        <v>-12</v>
+      </c>
       <c r="H131" s="20"/>
       <c r="I131" s="20"/>
       <c r="J131" s="4"/>
@@ -11558,14 +11651,22 @@
     </row>
     <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="41"/>
-      <c r="B132" s="14"/>
+      <c r="B132" s="14">
+        <v>46303</v>
+      </c>
       <c r="C132" s="48">
-        <v>127</v>
-      </c>
-      <c r="D132" s="81"/>
-      <c r="E132" s="82"/>
+        <v>126</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F132" s="19"/>
-      <c r="G132" s="20"/>
+      <c r="G132" s="20">
+        <v>-20</v>
+      </c>
       <c r="H132" s="20"/>
       <c r="I132" s="20"/>
       <c r="J132" s="4"/>
@@ -11574,14 +11675,22 @@
     </row>
     <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="41"/>
-      <c r="B133" s="14"/>
+      <c r="B133" s="14">
+        <v>46303</v>
+      </c>
       <c r="C133" s="48">
-        <v>128</v>
-      </c>
-      <c r="D133" s="37"/>
-      <c r="E133" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="D133" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="F133" s="19"/>
-      <c r="G133" s="20"/>
+      <c r="G133" s="20">
+        <v>-111.38</v>
+      </c>
       <c r="H133" s="20"/>
       <c r="I133" s="20"/>
       <c r="J133" s="4"/>
@@ -11592,10 +11701,10 @@
       <c r="A134" s="41"/>
       <c r="B134" s="14"/>
       <c r="C134" s="48">
-        <v>129</v>
-      </c>
-      <c r="D134" s="3"/>
-      <c r="E134" s="82"/>
+        <v>128</v>
+      </c>
+      <c r="D134" s="37"/>
+      <c r="E134" s="2"/>
       <c r="F134" s="19"/>
       <c r="G134" s="20"/>
       <c r="H134" s="20"/>
@@ -11608,10 +11717,10 @@
       <c r="A135" s="41"/>
       <c r="B135" s="14"/>
       <c r="C135" s="48">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D135" s="3"/>
-      <c r="E135" s="21"/>
+      <c r="E135" s="82"/>
       <c r="F135" s="19"/>
       <c r="G135" s="20"/>
       <c r="H135" s="20"/>
@@ -11624,10 +11733,10 @@
       <c r="A136" s="41"/>
       <c r="B136" s="14"/>
       <c r="C136" s="48">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D136" s="3"/>
-      <c r="E136" s="82"/>
+      <c r="E136" s="21"/>
       <c r="F136" s="19"/>
       <c r="G136" s="20"/>
       <c r="H136" s="20"/>
@@ -11640,10 +11749,10 @@
       <c r="A137" s="41"/>
       <c r="B137" s="14"/>
       <c r="C137" s="48">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D137" s="3"/>
-      <c r="E137" s="21"/>
+      <c r="E137" s="82"/>
       <c r="F137" s="19"/>
       <c r="G137" s="20"/>
       <c r="H137" s="20"/>
@@ -11656,7 +11765,7 @@
       <c r="A138" s="41"/>
       <c r="B138" s="14"/>
       <c r="C138" s="48">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="21"/>
@@ -11672,10 +11781,10 @@
       <c r="A139" s="41"/>
       <c r="B139" s="14"/>
       <c r="C139" s="48">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D139" s="3"/>
-      <c r="E139" s="82"/>
+      <c r="E139" s="21"/>
       <c r="F139" s="19"/>
       <c r="G139" s="20"/>
       <c r="H139" s="20"/>
@@ -11688,10 +11797,10 @@
       <c r="A140" s="41"/>
       <c r="B140" s="14"/>
       <c r="C140" s="48">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D140" s="3"/>
-      <c r="E140" s="21"/>
+      <c r="E140" s="82"/>
       <c r="F140" s="19"/>
       <c r="G140" s="20"/>
       <c r="H140" s="20"/>
@@ -11704,10 +11813,10 @@
       <c r="A141" s="41"/>
       <c r="B141" s="14"/>
       <c r="C141" s="48">
-        <v>136</v>
-      </c>
-      <c r="D141" s="81"/>
-      <c r="E141" s="82"/>
+        <v>135</v>
+      </c>
+      <c r="D141" s="3"/>
+      <c r="E141" s="21"/>
       <c r="F141" s="19"/>
       <c r="G141" s="20"/>
       <c r="H141" s="20"/>
@@ -11720,7 +11829,7 @@
       <c r="A142" s="41"/>
       <c r="B142" s="14"/>
       <c r="C142" s="48">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D142" s="81"/>
       <c r="E142" s="82"/>
@@ -11736,7 +11845,7 @@
       <c r="A143" s="41"/>
       <c r="B143" s="14"/>
       <c r="C143" s="48">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D143" s="81"/>
       <c r="E143" s="82"/>
@@ -11752,9 +11861,9 @@
       <c r="A144" s="41"/>
       <c r="B144" s="14"/>
       <c r="C144" s="48">
-        <v>139</v>
-      </c>
-      <c r="D144" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="D144" s="81"/>
       <c r="E144" s="82"/>
       <c r="F144" s="19"/>
       <c r="G144" s="20"/>
@@ -11768,7 +11877,7 @@
       <c r="A145" s="41"/>
       <c r="B145" s="14"/>
       <c r="C145" s="48">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="82"/>
@@ -11784,10 +11893,10 @@
       <c r="A146" s="41"/>
       <c r="B146" s="14"/>
       <c r="C146" s="48">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="2"/>
+      <c r="E146" s="82"/>
       <c r="F146" s="19"/>
       <c r="G146" s="20"/>
       <c r="H146" s="20"/>
@@ -11803,7 +11912,7 @@
         <v>141</v>
       </c>
       <c r="D147" s="3"/>
-      <c r="E147" s="82"/>
+      <c r="E147" s="2"/>
       <c r="F147" s="19"/>
       <c r="G147" s="20"/>
       <c r="H147" s="20"/>
@@ -11816,7 +11925,7 @@
       <c r="A148" s="41"/>
       <c r="B148" s="14"/>
       <c r="C148" s="48">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D148" s="3"/>
       <c r="E148" s="82"/>
@@ -11832,40 +11941,40 @@
       <c r="A149" s="41"/>
       <c r="B149" s="14"/>
       <c r="C149" s="48">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D149" s="3"/>
-      <c r="E149" s="21"/>
+      <c r="E149" s="82"/>
       <c r="F149" s="19"/>
       <c r="G149" s="20"/>
       <c r="H149" s="20"/>
       <c r="I149" s="20"/>
       <c r="J149" s="4"/>
       <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
     </row>
     <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="41"/>
       <c r="B150" s="14"/>
       <c r="C150" s="48">
-        <v>144</v>
-      </c>
-      <c r="D150" s="37"/>
-      <c r="E150" s="82"/>
+        <v>143</v>
+      </c>
+      <c r="D150" s="3"/>
+      <c r="E150" s="21"/>
       <c r="F150" s="19"/>
       <c r="G150" s="20"/>
       <c r="H150" s="20"/>
       <c r="I150" s="20"/>
       <c r="J150" s="4"/>
       <c r="K150" s="2"/>
-      <c r="L150" s="2"/>
     </row>
     <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="41"/>
       <c r="B151" s="14"/>
       <c r="C151" s="48">
-        <v>145</v>
-      </c>
-      <c r="D151" s="81"/>
+        <v>144</v>
+      </c>
+      <c r="D151" s="37"/>
       <c r="E151" s="82"/>
       <c r="F151" s="19"/>
       <c r="G151" s="20"/>
@@ -11879,9 +11988,9 @@
       <c r="A152" s="41"/>
       <c r="B152" s="14"/>
       <c r="C152" s="48">
-        <v>146</v>
-      </c>
-      <c r="D152" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="D152" s="81"/>
       <c r="E152" s="82"/>
       <c r="F152" s="19"/>
       <c r="G152" s="20"/>
@@ -11895,10 +12004,10 @@
       <c r="A153" s="41"/>
       <c r="B153" s="14"/>
       <c r="C153" s="48">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D153" s="3"/>
-      <c r="E153" s="21"/>
+      <c r="E153" s="82"/>
       <c r="F153" s="19"/>
       <c r="G153" s="20"/>
       <c r="H153" s="20"/>
@@ -11911,9 +12020,9 @@
       <c r="A154" s="41"/>
       <c r="B154" s="14"/>
       <c r="C154" s="48">
-        <v>148</v>
-      </c>
-      <c r="D154" s="37"/>
+        <v>147</v>
+      </c>
+      <c r="D154" s="3"/>
       <c r="E154" s="21"/>
       <c r="F154" s="19"/>
       <c r="G154" s="20"/>
@@ -11943,10 +12052,10 @@
       <c r="A156" s="41"/>
       <c r="B156" s="14"/>
       <c r="C156" s="48">
-        <v>149</v>
-      </c>
-      <c r="D156" s="3"/>
-      <c r="E156" s="82"/>
+        <v>148</v>
+      </c>
+      <c r="D156" s="37"/>
+      <c r="E156" s="21"/>
       <c r="F156" s="19"/>
       <c r="G156" s="20"/>
       <c r="H156" s="20"/>
@@ -11959,9 +12068,9 @@
       <c r="A157" s="41"/>
       <c r="B157" s="14"/>
       <c r="C157" s="48">
-        <v>149.69999999999999</v>
-      </c>
-      <c r="D157" s="81"/>
+        <v>149</v>
+      </c>
+      <c r="D157" s="3"/>
       <c r="E157" s="82"/>
       <c r="F157" s="19"/>
       <c r="G157" s="20"/>
@@ -11975,7 +12084,7 @@
       <c r="A158" s="41"/>
       <c r="B158" s="14"/>
       <c r="C158" s="48">
-        <v>151</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="D158" s="81"/>
       <c r="E158" s="82"/>
@@ -11991,10 +12100,10 @@
       <c r="A159" s="41"/>
       <c r="B159" s="14"/>
       <c r="C159" s="48">
-        <v>152</v>
-      </c>
-      <c r="D159" s="37"/>
-      <c r="E159" s="21"/>
+        <v>151</v>
+      </c>
+      <c r="D159" s="81"/>
+      <c r="E159" s="82"/>
       <c r="F159" s="19"/>
       <c r="G159" s="20"/>
       <c r="H159" s="20"/>
@@ -12007,7 +12116,7 @@
       <c r="A160" s="41"/>
       <c r="B160" s="14"/>
       <c r="C160" s="48">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D160" s="37"/>
       <c r="E160" s="21"/>
@@ -12023,7 +12132,7 @@
       <c r="A161" s="41"/>
       <c r="B161" s="14"/>
       <c r="C161" s="48">
-        <v>154.03</v>
+        <v>153</v>
       </c>
       <c r="D161" s="37"/>
       <c r="E161" s="21"/>
@@ -12039,7 +12148,7 @@
       <c r="A162" s="41"/>
       <c r="B162" s="14"/>
       <c r="C162" s="48">
-        <v>155.06</v>
+        <v>154.03</v>
       </c>
       <c r="D162" s="37"/>
       <c r="E162" s="21"/>
@@ -12055,7 +12164,7 @@
       <c r="A163" s="41"/>
       <c r="B163" s="14"/>
       <c r="C163" s="48">
-        <v>156.09</v>
+        <v>155.06</v>
       </c>
       <c r="D163" s="37"/>
       <c r="E163" s="21"/>
@@ -12071,7 +12180,7 @@
       <c r="A164" s="41"/>
       <c r="B164" s="14"/>
       <c r="C164" s="48">
-        <v>157.12</v>
+        <v>156.09</v>
       </c>
       <c r="D164" s="37"/>
       <c r="E164" s="21"/>
@@ -12087,10 +12196,10 @@
       <c r="A165" s="41"/>
       <c r="B165" s="14"/>
       <c r="C165" s="48">
-        <v>158.15</v>
+        <v>157.12</v>
       </c>
       <c r="D165" s="37"/>
-      <c r="E165" s="18"/>
+      <c r="E165" s="21"/>
       <c r="F165" s="19"/>
       <c r="G165" s="20"/>
       <c r="H165" s="20"/>
@@ -12103,10 +12212,10 @@
       <c r="A166" s="41"/>
       <c r="B166" s="14"/>
       <c r="C166" s="48">
-        <v>159.18</v>
+        <v>158.15</v>
       </c>
       <c r="D166" s="37"/>
-      <c r="E166" s="21"/>
+      <c r="E166" s="18"/>
       <c r="F166" s="19"/>
       <c r="G166" s="20"/>
       <c r="H166" s="20"/>
@@ -12119,11 +12228,11 @@
       <c r="A167" s="41"/>
       <c r="B167" s="14"/>
       <c r="C167" s="48">
-        <v>160.21</v>
+        <v>159.18</v>
       </c>
       <c r="D167" s="37"/>
       <c r="E167" s="21"/>
-      <c r="F167" s="20"/>
+      <c r="F167" s="19"/>
       <c r="G167" s="20"/>
       <c r="H167" s="20"/>
       <c r="I167" s="20"/>
@@ -12135,11 +12244,11 @@
       <c r="A168" s="41"/>
       <c r="B168" s="14"/>
       <c r="C168" s="48">
-        <v>161.24</v>
+        <v>160.21</v>
       </c>
       <c r="D168" s="37"/>
       <c r="E168" s="21"/>
-      <c r="F168" s="19"/>
+      <c r="F168" s="20"/>
       <c r="G168" s="20"/>
       <c r="H168" s="20"/>
       <c r="I168" s="20"/>
@@ -12151,10 +12260,10 @@
       <c r="A169" s="41"/>
       <c r="B169" s="14"/>
       <c r="C169" s="48">
-        <v>162.27000000000001</v>
-      </c>
-      <c r="D169" s="3"/>
-      <c r="E169" s="82"/>
+        <v>161.24</v>
+      </c>
+      <c r="D169" s="37"/>
+      <c r="E169" s="21"/>
       <c r="F169" s="19"/>
       <c r="G169" s="20"/>
       <c r="H169" s="20"/>
@@ -12167,10 +12276,10 @@
       <c r="A170" s="41"/>
       <c r="B170" s="14"/>
       <c r="C170" s="48">
-        <v>163.30000000000001</v>
-      </c>
-      <c r="D170" s="37"/>
-      <c r="E170" s="21"/>
+        <v>162.27000000000001</v>
+      </c>
+      <c r="D170" s="3"/>
+      <c r="E170" s="82"/>
       <c r="F170" s="19"/>
       <c r="G170" s="20"/>
       <c r="H170" s="20"/>
@@ -12183,10 +12292,10 @@
       <c r="A171" s="41"/>
       <c r="B171" s="14"/>
       <c r="C171" s="48">
-        <v>164.33</v>
+        <v>163.30000000000001</v>
       </c>
       <c r="D171" s="37"/>
-      <c r="E171" s="18"/>
+      <c r="E171" s="21"/>
       <c r="F171" s="19"/>
       <c r="G171" s="20"/>
       <c r="H171" s="20"/>
@@ -12199,10 +12308,10 @@
       <c r="A172" s="41"/>
       <c r="B172" s="14"/>
       <c r="C172" s="48">
-        <v>165.36</v>
+        <v>164.33</v>
       </c>
       <c r="D172" s="37"/>
-      <c r="E172" s="21"/>
+      <c r="E172" s="18"/>
       <c r="F172" s="19"/>
       <c r="G172" s="20"/>
       <c r="H172" s="20"/>
@@ -12215,10 +12324,10 @@
       <c r="A173" s="41"/>
       <c r="B173" s="14"/>
       <c r="C173" s="48">
-        <v>166.39</v>
-      </c>
-      <c r="D173" s="15"/>
-      <c r="E173" s="18"/>
+        <v>165.36</v>
+      </c>
+      <c r="D173" s="37"/>
+      <c r="E173" s="21"/>
       <c r="F173" s="19"/>
       <c r="G173" s="20"/>
       <c r="H173" s="20"/>
@@ -12231,7 +12340,7 @@
       <c r="A174" s="41"/>
       <c r="B174" s="14"/>
       <c r="C174" s="48">
-        <v>167.42</v>
+        <v>166.39</v>
       </c>
       <c r="D174" s="15"/>
       <c r="E174" s="18"/>
@@ -12247,7 +12356,7 @@
       <c r="A175" s="41"/>
       <c r="B175" s="14"/>
       <c r="C175" s="48">
-        <v>168.45</v>
+        <v>167.42</v>
       </c>
       <c r="D175" s="15"/>
       <c r="E175" s="18"/>
@@ -12255,7 +12364,7 @@
       <c r="G175" s="20"/>
       <c r="H175" s="20"/>
       <c r="I175" s="20"/>
-      <c r="J175" s="44"/>
+      <c r="J175" s="4"/>
       <c r="K175" s="2"/>
       <c r="L175" s="2"/>
     </row>
@@ -12263,7 +12372,7 @@
       <c r="A176" s="41"/>
       <c r="B176" s="14"/>
       <c r="C176" s="48">
-        <v>169.48</v>
+        <v>168.45</v>
       </c>
       <c r="D176" s="15"/>
       <c r="E176" s="18"/>
@@ -12279,7 +12388,7 @@
       <c r="A177" s="41"/>
       <c r="B177" s="14"/>
       <c r="C177" s="48">
-        <v>170.51</v>
+        <v>169.48</v>
       </c>
       <c r="D177" s="15"/>
       <c r="E177" s="18"/>
@@ -12294,8 +12403,10 @@
     <row r="178" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="41"/>
       <c r="B178" s="14"/>
-      <c r="C178" s="48"/>
-      <c r="D178" s="37"/>
+      <c r="C178" s="48">
+        <v>170.51</v>
+      </c>
+      <c r="D178" s="15"/>
       <c r="E178" s="18"/>
       <c r="F178" s="19"/>
       <c r="G178" s="20"/>
@@ -12304,46 +12415,46 @@
       <c r="J178" s="44"/>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
-      <c r="IL178"/>
     </row>
     <row r="179" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="42"/>
-      <c r="B179" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C179" s="49"/>
-      <c r="D179" s="29"/>
-      <c r="E179" s="30"/>
-      <c r="F179" s="31">
-        <f>SUM(F3:F178)</f>
-        <v>0</v>
-      </c>
-      <c r="G179" s="32">
-        <f>SUM(G3:G178)</f>
-        <v>-5216.6299999999947</v>
-      </c>
-      <c r="H179" s="32">
-        <f>SUM(H3:H178)</f>
-        <v>0</v>
-      </c>
-      <c r="I179" s="32">
-        <f>SUM(I3:I178)</f>
-        <v>-4875.21</v>
-      </c>
-      <c r="J179" s="2"/>
+      <c r="A179" s="41"/>
+      <c r="B179" s="14"/>
+      <c r="C179" s="48"/>
+      <c r="D179" s="37"/>
+      <c r="E179" s="18"/>
+      <c r="F179" s="19"/>
+      <c r="G179" s="20"/>
+      <c r="H179" s="20"/>
+      <c r="I179" s="20"/>
+      <c r="J179" s="44"/>
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
+      <c r="IL179"/>
     </row>
     <row r="180" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="42"/>
-      <c r="B180" s="17"/>
-      <c r="C180" s="17"/>
-      <c r="D180" s="17"/>
-      <c r="E180" s="17"/>
-      <c r="F180" s="17"/>
-      <c r="G180" s="17"/>
-      <c r="H180" s="17"/>
-      <c r="I180" s="17"/>
+      <c r="B180" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="49"/>
+      <c r="D180" s="29"/>
+      <c r="E180" s="30"/>
+      <c r="F180" s="31">
+        <f>SUM(F3:F179)</f>
+        <v>0</v>
+      </c>
+      <c r="G180" s="32">
+        <f>SUM(G3:G179)</f>
+        <v>-5504.979999999995</v>
+      </c>
+      <c r="H180" s="32">
+        <f>SUM(H3:H179)</f>
+        <v>0</v>
+      </c>
+      <c r="I180" s="32">
+        <f>SUM(I3:I179)</f>
+        <v>-4882.71</v>
+      </c>
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
@@ -13214,6 +13325,7 @@
       <c r="I242" s="17"/>
       <c r="J242" s="2"/>
       <c r="K242" s="2"/>
+      <c r="L242" s="2"/>
     </row>
     <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="42"/>
@@ -13226,198 +13338,211 @@
       <c r="H243" s="17"/>
       <c r="I243" s="17"/>
       <c r="J243" s="2"/>
+      <c r="K243" s="2"/>
     </row>
     <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="42"/>
       <c r="B244" s="17"/>
       <c r="C244" s="17"/>
+      <c r="D244" s="17"/>
+      <c r="E244" s="17"/>
+      <c r="F244" s="17"/>
+      <c r="G244" s="17"/>
+      <c r="H244" s="17"/>
       <c r="I244" s="17"/>
+      <c r="J244" s="2"/>
     </row>
     <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B245" s="17"/>
+      <c r="C245" s="17"/>
       <c r="I245" s="17"/>
     </row>
+    <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B246" s="17"/>
+      <c r="I246" s="17"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:J174" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="B2:J175" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A243 E33 E134:E145">
-    <cfRule type="cellIs" dxfId="34" priority="501" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A3:A244 E33 E135:E146">
+    <cfRule type="cellIs" dxfId="34" priority="502" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B130:B143">
-    <cfRule type="cellIs" dxfId="33" priority="484" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="B132:B144">
+    <cfRule type="cellIs" dxfId="33" priority="485" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B157:B245">
-    <cfRule type="cellIs" dxfId="32" priority="41" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="B158:B246">
+    <cfRule type="cellIs" dxfId="32" priority="42" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C156 C158 C160 C162 C164 C166 C168 C174 C176">
-    <cfRule type="cellIs" dxfId="31" priority="42" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C157 C159 C161 C163 C165 C167 C169 C175 C177">
+    <cfRule type="cellIs" dxfId="31" priority="43" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C178:C244 J180 I180:I245">
-    <cfRule type="cellIs" dxfId="30" priority="731" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C179:C245 J181 I181:I246">
+    <cfRule type="cellIs" dxfId="30" priority="732" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D133">
-    <cfRule type="cellIs" dxfId="29" priority="499" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D134">
+    <cfRule type="cellIs" dxfId="29" priority="500" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D150">
-    <cfRule type="cellIs" dxfId="28" priority="86" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D151">
+    <cfRule type="cellIs" dxfId="28" priority="87" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D154:D155">
-    <cfRule type="cellIs" dxfId="27" priority="470" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D155:D156">
+    <cfRule type="cellIs" dxfId="27" priority="471" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D159:D164">
-    <cfRule type="cellIs" dxfId="26" priority="27" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D160:D165">
+    <cfRule type="cellIs" dxfId="26" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D165:E166 D167:D168 C170:D170 D171:E171 C172:D172">
-    <cfRule type="cellIs" dxfId="25" priority="34" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D166:E167 D168:D169 C171:D171 D172:E172 C173:D173">
+    <cfRule type="cellIs" dxfId="25" priority="35" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D178:E180">
-    <cfRule type="cellIs" dxfId="24" priority="36" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D179:E181">
+    <cfRule type="cellIs" dxfId="24" priority="37" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D180:H243">
-    <cfRule type="cellIs" dxfId="23" priority="683" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D181:H244">
+    <cfRule type="cellIs" dxfId="23" priority="684" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E147:E164">
-    <cfRule type="cellIs" dxfId="22" priority="22" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E148:E165">
+    <cfRule type="cellIs" dxfId="22" priority="23" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="21" priority="18" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="19" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="20" priority="19" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="20" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="19" priority="17" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="18" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58:E59">
-    <cfRule type="cellIs" dxfId="18" priority="16" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61">
-    <cfRule type="cellIs" dxfId="17" priority="15" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="16" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E64">
-    <cfRule type="cellIs" dxfId="16" priority="14" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="15" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E66:E68">
-    <cfRule type="cellIs" dxfId="15" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="14" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72">
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E76:E81 E87:E89 E112:E114 E116">
-    <cfRule type="cellIs" dxfId="13" priority="8" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="9" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E85">
-    <cfRule type="cellIs" dxfId="12" priority="7" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E109:E110">
-    <cfRule type="cellIs" dxfId="11" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E122:E125 E127:E132">
-    <cfRule type="cellIs" dxfId="10" priority="3" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E122:E131">
+    <cfRule type="cellIs" dxfId="10" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E167:E170">
-    <cfRule type="cellIs" dxfId="9" priority="24" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E168:E171">
+    <cfRule type="cellIs" dxfId="9" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E172:E177">
-    <cfRule type="cellIs" dxfId="8" priority="23" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E173:E178">
+    <cfRule type="cellIs" dxfId="8" priority="24" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="7" priority="21" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="22" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F77">
-    <cfRule type="cellIs" dxfId="6" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F87">
-    <cfRule type="cellIs" dxfId="5" priority="6" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99:F100">
-    <cfRule type="cellIs" dxfId="4" priority="144" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="145" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="cellIs" dxfId="2" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F125">
-    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E126">
+  <conditionalFormatting sqref="F131">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E147:E178 E134:E145 E58:E59 E72 E61 E64 E66:E68 E76:E81 E85 E87:E89 E109:E110 E112:E114 E116 E122:E132" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E148:E179 E135:E146 E58:E59 E72 E61 E64 E66:E68 E76:E81 E85 E87:E89 E109:E110 E112:E114 E116 E122:E131" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$L$1:$L$19</formula1>
     </dataValidation>
   </dataValidations>
